--- a/naver-place-crawler/results_health/판교_PT.xlsx
+++ b/naver-place-crawler/results_health/판교_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="Q2" t="n">
         <v>319</v>
       </c>
       <c r="R2" t="n">
-        <v>2845</v>
+        <v>2844</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -653,34 +653,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>원팀짐</t>
+          <t>바로선운동센터 판교점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>oneteamgym-@naver.com</t>
+          <t>coolksh11@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>031-702-2070</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 128 7층 701호</t>
+          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oneteamgym1</t>
+          <t>https://blog.naver.com/coolksh11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +691,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>490</v>
+        <v>19</v>
       </c>
       <c r="Q3" t="n">
-        <v>288</v>
+        <v>148</v>
       </c>
       <c r="R3" t="n">
-        <v>778</v>
+        <v>167</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +726,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1973455447</t>
+          <t>2015061102</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973455447</t>
+          <t>https://m.place.naver.com/place/2015061102</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,25 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>바로선운동센터 판교점</t>
+          <t>리조트휘트니스 PT 판교점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>coolksh11@naver.com</t>
+          <t>resort_5@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1438-0677</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/coolksh11</t>
+          <t>https://www.instagram.com/resortfitness__pangyo/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>19</v>
+        <v>411</v>
       </c>
       <c r="Q4" t="n">
-        <v>144</v>
+        <v>714</v>
       </c>
       <c r="R4" t="n">
-        <v>163</v>
+        <v>1125</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2015061102</t>
+          <t>35524502</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015061102</t>
+          <t>https://m.place.naver.com/place/35524502</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -842,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>리조트휘트니스 PT 판교점</t>
+          <t>업투 휘트니스 분당판교점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>resort_5@naver.com</t>
+          <t>uptofitness-@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1438-0677</t>
+          <t>0507-1343-8274</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+          <t>https://blog.naver.com/uptofitness-</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>410</v>
+        <v>615</v>
       </c>
       <c r="Q5" t="n">
-        <v>714</v>
+        <v>289</v>
       </c>
       <c r="R5" t="n">
-        <v>1124</v>
+        <v>904</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,12 +914,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>35524502</t>
+          <t>1928497638</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35524502</t>
+          <t>https://m.place.naver.com/place/1928497638</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -936,39 +936,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>업투 휘트니스 분당판교점</t>
+          <t>H GYM PT GT 판교2호점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>uptofitness-@naver.com</t>
+          <t>hgym9408@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1343-8274</t>
+          <t>0507-1353-9408</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/uptofitness-</t>
+          <t>https://hgym.imweb.me</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>616</v>
+        <v>278</v>
       </c>
       <c r="Q6" t="n">
-        <v>289</v>
+        <v>418</v>
       </c>
       <c r="R6" t="n">
-        <v>905</v>
+        <v>696</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1928497638</t>
+          <t>1850894755</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928497638</t>
+          <t>https://m.place.naver.com/place/1850894755</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1030,39 +1030,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H GYM PT GT 판교2호점</t>
+          <t>쿼드짐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hgym9408@naver.com</t>
+          <t>quadgym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1353-9408</t>
+          <t>0507-1303-9415</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 233 302호</t>
+          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://hgym.imweb.me</t>
+          <t>https://blog.naver.com/quadgym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>278</v>
+        <v>81</v>
       </c>
       <c r="Q7" t="n">
-        <v>418</v>
+        <v>102</v>
       </c>
       <c r="R7" t="n">
-        <v>696</v>
+        <v>183</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1850894755</t>
+          <t>1759307500</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850894755</t>
+          <t>https://m.place.naver.com/place/1759307500</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1124,38 +1124,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 판교</t>
+          <t>베스트바디발란스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>wjdwktnso@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1417-1133</t>
+          <t>0507-1402-7136</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://blog.naver.com/wjdwktnso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1176,22 +1172,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2029680813</t>
+          <t>36428321</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
+          <t>https://m.place.naver.com/place/36428321</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,38 +1213,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1329-4325</t>
-        </is>
-      </c>
+          <t>let_me_pt_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://blog.naver.com/let_me_pt_official</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,7 +1262,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1283,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1758</v>
+        <v>79</v>
       </c>
       <c r="Q9" t="n">
-        <v>244</v>
+        <v>49</v>
       </c>
       <c r="R9" t="n">
-        <v>2002</v>
+        <v>128</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1286,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1049956503</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1049956503</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,38 +1308,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 판교벤처타운</t>
+          <t>프로원핏 정자점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>betabros-@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1304-0676</t>
+          <t>0507-1466-0213</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
+          <t>경기도 성남시 분당구 정자로 13 3층 310호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://blog.naver.com/betabros-</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1372,7 +1356,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1381,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,12 +1380,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2030115135</t>
+          <t>1322454491</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2030115135</t>
+          <t>https://m.place.naver.com/place/1322454491</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1411,36 +1395,20 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>더바디짐 PT 분당수내점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>thebodyptgym@naver.com</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1387-7676</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로46번길 11 대덕글로리빌딩 5층 더바디짐</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thebodyptgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1450,12 +1418,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1471,17 +1439,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1709</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,12 +1458,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>36666737</t>
+          <t>2600001</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36666737</t>
+          <t>https://m.place.naver.com/place/2600001</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1505,36 +1473,20 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>쿼드짐</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>quadgym@naver.com</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1303-9415</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/quadgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1544,12 +1496,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1565,17 +1517,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1584,15 +1536,249 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1759307500</t>
+          <t>7167332</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759307500</t>
+          <t>https://m.place.naver.com/place/7167332</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>7258722</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7258722</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>7142668</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7142668</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>7583905</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7583905</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/판교_PT.xlsx
+++ b/naver-place-crawler/results_health/판교_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>팀제이맥스 피티 서현점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>teamjmax_sh@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>031-702-8296</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://blog.naver.com/teamjmax_sh</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2525</v>
+        <v>911</v>
       </c>
       <c r="Q2" t="n">
-        <v>319</v>
+        <v>549</v>
       </c>
       <c r="R2" t="n">
-        <v>2844</v>
+        <v>1460</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1639683746</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1639683746</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,25 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>바로선운동센터 판교점</t>
+          <t>구스짐 PT 판교점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>coolksh11@naver.com</t>
+          <t>chlgudrn1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1465-9683</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/coolksh11</t>
+          <t>https://www.instagram.com/9s_gym_pangyo/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -691,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -711,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="Q3" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="R3" t="n">
-        <v>167</v>
+        <v>304</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2015061102</t>
+          <t>1088776551</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015061102</t>
+          <t>https://m.place.naver.com/place/1088776551</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -748,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>리조트휘트니스 PT 판교점</t>
+          <t>에너지플로우짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>resort_5@naver.com</t>
+          <t>exerscience@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1438-0677</t>
+          <t>0507-1346-9129</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B126-1호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+          <t>https://energyflowlab.my.canva.site</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>411</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>714</v>
+        <v>38</v>
       </c>
       <c r="R4" t="n">
-        <v>1125</v>
+        <v>39</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>35524502</t>
+          <t>1846760075</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35524502</t>
+          <t>https://m.place.naver.com/place/1846760075</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -842,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>업투 휘트니스 분당판교점</t>
+          <t>캔들짐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uptofitness-@naver.com</t>
+          <t>tnghkd213@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1343-8274</t>
+          <t>0507-1333-7650</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 판교푸르지오월드마크 제2-17호 캔들짐</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/uptofitness-</t>
+          <t>https://www.instagram.com/Candlegymfitness</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -879,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>615</v>
+        <v>6</v>
       </c>
       <c r="Q5" t="n">
-        <v>289</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>904</v>
+        <v>14</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1928497638</t>
+          <t>1242676842</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928497638</t>
+          <t>https://m.place.naver.com/place/1242676842</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -936,44 +940,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H GYM PT GT 판교2호점</t>
+          <t>솔리드짐 PT 수내점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hgym9408@naver.com</t>
+          <t>ppapers@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1353-9408</t>
+          <t>0507-1420-7858</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 233 302호</t>
+          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://hgym.imweb.me</t>
+          <t>https://www.instagram.com/solid_gym1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>278</v>
+        <v>145</v>
       </c>
       <c r="Q6" t="n">
-        <v>418</v>
+        <v>649</v>
       </c>
       <c r="R6" t="n">
-        <v>696</v>
+        <v>794</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1850894755</t>
+          <t>1205679892</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850894755</t>
+          <t>https://m.place.naver.com/place/1205679892</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>쿼드짐</t>
+          <t>핏앤클래시 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>quadgym@naver.com</t>
+          <t>fitclassy22@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1303-9415</t>
+          <t>0507-1325-5251</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
+          <t>경기도 성남시 분당구 서판교로 154 낙생빌딩 201호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/quadgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1062,20 +1066,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45ryz</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1087,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="Q7" t="n">
-        <v>102</v>
+        <v>22</v>
       </c>
       <c r="R7" t="n">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1759307500</t>
+          <t>1283224823</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759307500</t>
+          <t>https://m.place.naver.com/place/1283224823</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>베스트바디발란스</t>
+          <t>여성전용 비조 필라PT 자이로토닉</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>wjdwktnso@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1402-7136</t>
-        </is>
-      </c>
+          <t>viyulgallery@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>themosttimes@tmt.co.kr</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
+          <t>경기도 성남시 분당구 운중로 132</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjdwktnso</t>
+          <t>https://www.themosttimes.co.kr/43811</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1161,15 +1169,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4642d</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1181,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="Q8" t="n">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c r="R8" t="n">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,52 +1208,56 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36428321</t>
+          <t>1600591794</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428321</t>
+          <t>https://m.place.naver.com/place/1600591794</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>실내골프연습장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
+          <t>철인짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>let_me_pt_official@naver.com</t>
+          <t>chulingym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1475-0968</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
+          <t>경기도 성남시 분당구 운중로 141 우리은행 건물 9층 철인짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/let_me_pt_official</t>
+          <t>http://pf.kakao.com/_KZkEG</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1251,7 +1267,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1262,7 +1278,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1271,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="R9" t="n">
-        <v>128</v>
+        <v>20</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1302,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1049956503</t>
+          <t>1883390700</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049956503</t>
+          <t>https://m.place.naver.com/place/1883390700</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1324,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로원핏 정자점</t>
+          <t>바디센서리 판교점 헬스PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>betabros-@naver.com</t>
+          <t>bodysensory@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1466-0213</t>
+          <t>0507-1344-2096</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자로 13 3층 310호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 41 프라임스퀘어 10층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/betabros-</t>
+          <t>https://www.instagram.com/BumGi</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1345,7 +1361,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1365,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>292</v>
       </c>
       <c r="R10" t="n">
-        <v>49</v>
+        <v>338</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,30 +1396,46 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1322454491</t>
+          <t>1786901360</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1322454491</t>
+          <t>https://m.place.naver.com/place/1786901360</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>비아핏</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>viafit@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1379-7507</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 판교대장로7길 15-2 지하1층,지상1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1428,10 +1460,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w37pnp4</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1439,17 +1475,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1458,30 +1494,46 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2600001</t>
+          <t>1772663783</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2600001</t>
+          <t>https://m.place.naver.com/place/1772663783</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>린바디핏 PT 판교본점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>leanbodyfitv2@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1302-8312</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 지하113호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1506,13 +1558,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3fqoyd</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1521,13 +1577,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1536,30 +1592,46 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>7167332</t>
+          <t>1699238533</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7167332</t>
+          <t>https://m.place.naver.com/place/1699238533</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>스윗바디</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>superfly3@naver.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>031-701-4327</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 판교역로2번길 36 1층 스윗바디</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1584,10 +1656,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5whn9</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1595,17 +1671,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1614,40 +1690,56 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>7258722</t>
+          <t>20364482</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7258722</t>
+          <t>https://m.place.naver.com/place/20364482</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H GYM PT GT 운중점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1344-9408</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 운중로188번길 8 1층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://hgym.co.kr</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1657,15 +1749,19 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gmmz</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>X</t>
@@ -1673,17 +1769,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1692,45 +1788,61 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>7142668</t>
+          <t>1970444039</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7142668</t>
+          <t>https://m.place.naver.com/place/1970444039</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>피티세븐 퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>body2balance@naver.com</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1400-9428</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.pts7.com</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1740,47 +1852,5945 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4bej5</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
+        <v>299</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>291</v>
+      </c>
+      <c r="R15" t="n">
+        <v>590</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>13093618</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13093618</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>리,무브먼트</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>sujin6735@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1310-5661</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ag69</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>242</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>245</v>
+      </c>
+      <c r="R16" t="n">
+        <v>487</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1149465061</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1149465061</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H GYM PT GT 판교2호점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1353-9408</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://hgym.imweb.me</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47alh</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>278</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>419</v>
+      </c>
+      <c r="R17" t="n">
+        <v>697</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1850894755</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850894755</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>엑서사이언스짐</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>exerscience@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 240 삼환하이펙스A동 B1층 B117-1호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vur6</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>143</v>
+      </c>
+      <c r="R18" t="n">
+        <v>150</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1746641680</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1746641680</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>바른몸 재활PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>wise_body_care@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1491-9925</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 376 6층 605호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5uzxa</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>35</v>
+      </c>
+      <c r="R19" t="n">
+        <v>116</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1253283857</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1253283857</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>복싱,권투장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>카운터복싱 판교대장점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>counterboxing13@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1365-8859</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로8길 8 303호, 304호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u3lu</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>210</v>
+      </c>
+      <c r="R20" t="n">
+        <v>215</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1889442444</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1889442444</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>유앤바디PT 분당수내점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>unbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>031-714-4729</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 12 세인프라자 402호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4b6la</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>164</v>
+      </c>
+      <c r="R21" t="n">
+        <v>282</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1853394852</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1853394852</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>제로업PT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>linefit91@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>031-623-2775</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 느티로 16 7층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>765</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>687</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1452</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1975822360</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1975822360</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>버핏그라운드 PT 판교벤처타운</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1304-0676</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.butfitground.com/4steppt</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R23" t="n">
+        <v>2</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2030115135</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2030115135</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>어반피트</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>urbanfit_@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1357-0997</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 128 601,602호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44gs9</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>27</v>
+      </c>
+      <c r="R24" t="n">
+        <v>60</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1138293980</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1138293980</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>원프로짐PT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>onepro_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1304-9363</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로 164 훼미리프라자 402호</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wd5irjz</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>34</v>
+      </c>
+      <c r="R25" t="n">
+        <v>48</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1663447864</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1663447864</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>핏불짐 판교점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>fitbullgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1430-9683</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2 3층 304호</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/fitbullgym</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eqla</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>283</v>
+      </c>
+      <c r="R26" t="n">
+        <v>375</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>37814535</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37814535</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>블랙스미스짐 헬스PT 판교점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>emmaholic1@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1352-4388</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 지하2층 비2147호, 비2148호</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>http://blacksmithgym.kr/</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41p6u</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>194</v>
+      </c>
+      <c r="R27" t="n">
+        <v>301</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1462760829</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1462760829</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>유밸런스</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>moveez@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1496-8969</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 140 203호</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xvy6</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>103</v>
+      </c>
+      <c r="R28" t="n">
+        <v>138</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1069284280</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1069284280</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>버핏그라운드 PT 판교</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1417-1133</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.butfitground.com/4steppt</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
         <v>0</v>
       </c>
-      <c r="R15" t="n">
+      <c r="Q29" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>7583905</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7583905</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2029680813</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2029680813</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>휘트니스클럽S 수내점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>fitnessclubs12@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1311-1188</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 11 5층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49zvx</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>309</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>917</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1226</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1228787055</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1228787055</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>로이핏1인PT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>lyrdyd11@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로6길 10 4층 ROYFIT STUDIO</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h728</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>526</v>
+      </c>
+      <c r="R31" t="n">
+        <v>555</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1191780262</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1191780262</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>스윕피티필라테스</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>songj1919@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 상가동 1층 105,106호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcc6zd5</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>102</v>
+      </c>
+      <c r="R32" t="n">
+        <v>119</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1734844856</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1734844856</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>판교피트니스센터</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>towershift@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1343-5171</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로289번길 20 3층 판교피트니스센터</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>13</v>
+      </c>
+      <c r="R33" t="n">
+        <v>21</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1874121479</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1874121479</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>포랩 이즈메디운동센터</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>for_lab2017@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1432-1575</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc1hom</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>158</v>
+      </c>
+      <c r="R34" t="n">
+        <v>445</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>917204514</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/917204514</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>근육연구소</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>musclelab_9609@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1492-9193</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 109 A동 B212호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>172</v>
+      </c>
+      <c r="R35" t="n">
+        <v>177</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1655228047</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1655228047</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>halogym02@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1315-8840</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfevb4</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>663</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>925</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1588</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1806695299</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1806695299</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>좋은습관PTSTUDIO 판교운중</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>goodhabitpg@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1480-0677</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 142 6층</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wyz9</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>29</v>
+      </c>
+      <c r="R37" t="n">
+        <v>93</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1070284726</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1070284726</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>커스텀PT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>custom_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1485-0376</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로779번길 48 3층 304호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/custom_pt</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>26</v>
+      </c>
+      <c r="R38" t="n">
+        <v>186</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1204743611</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1204743611</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>하이퀄짐 헬스PT 판교점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>highqualgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1364-9601</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 128 2층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w406tf</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>103</v>
+      </c>
+      <c r="R39" t="n">
+        <v>161</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1012638231</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1012638231</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>업투 휘트니스 분당판교점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>uptofitness-@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1343-8274</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ijhg</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>618</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>291</v>
+      </c>
+      <c r="R40" t="n">
+        <v>909</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1928497638</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1928497638</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>베러댄 휘트니스 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>56zqrwcwsv@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1438-9698</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o2xj</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2078</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2460</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1013682807</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1013682807</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>헬스보이짐&amp;필라걸 수내점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>healthboy40@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1380-2239</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4laa0</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>969</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>734</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1703</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1973151166</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1973151166</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>커스텀핏 PT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>customfitpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>031-8016-5677</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 123 마크시티 오렌지동 3층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>5</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>35644006</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35644006</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>써트짐 PT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>certgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1367-7665</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로214번길 8 207호(수내동, MS프라자)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dpxc</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>237</v>
+      </c>
+      <c r="R44" t="n">
+        <v>286</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1331332549</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1331332549</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H GYM PT 대장3호점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1329-9408</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로 84 304호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://hgym.co.kr</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4aih7</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>111</v>
+      </c>
+      <c r="R45" t="n">
+        <v>222</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1027491629</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1027491629</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>바디수</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>lovelygodus@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>070-8802-9000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로44번길 15 101호</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>http://www.bodysoo.co.kr/</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>11</v>
+      </c>
+      <c r="R46" t="n">
+        <v>16</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>32497004</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32497004</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>바디브레인PT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>skemfisz1@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1329-8163</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로779번길 52 502호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jjaejjae0206</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>80</v>
+      </c>
+      <c r="R47" t="n">
+        <v>166</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1075198509</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1075198509</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>레조나헬스랩PT 서판교점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>resonar_healthlab@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1411-1104</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42t22</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>202</v>
+      </c>
+      <c r="R48" t="n">
+        <v>258</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1644348689</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1644348689</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>건강한 운동 연구소</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>brave082@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1347-2906</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로44번길 3-14 102호 건강한 운동 연구소</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>6</v>
+      </c>
+      <c r="R49" t="n">
+        <v>20</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1780907875</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1780907875</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PDC스포츠센터</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>spxkzjs12@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>031-8060-0377</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 242 판교디지털센터 A동 2층 PDC스포츠센터</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>19</v>
+      </c>
+      <c r="R50" t="n">
+        <v>71</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1057141943</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1057141943</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>파우즈더바디 이매점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>pausethebodytraining@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1425-7282</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 432 4층 1호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pause_the_body_imae</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>9</v>
+      </c>
+      <c r="R51" t="n">
+        <v>71</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1577244696</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1577244696</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>뉴로스위칭 판교본점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>team_hero@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1403-9311</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1A 제2층 216호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>41</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>34896927</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34896927</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>뱅핏 PT 판교운중점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>bangfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1345-4609</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 122 골드클래스 8층 801호, 802호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40lij</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>245</v>
+      </c>
+      <c r="R53" t="n">
+        <v>310</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1890400282</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1890400282</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>스포애니 서현역점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>spoany22@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>031-706-8522</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40q6m</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>948</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2034</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2982</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>13025013</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13025013</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>R31 필라테스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>r31functional@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1489-0374</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 58 나이스프라자 4층 402호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w454nh</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>24</v>
+      </c>
+      <c r="R55" t="n">
+        <v>102</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1262189356</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1262189356</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D gym PT 수내역점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>hyenggoo1@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1438-1374</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로200번길 34 205, 206호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40pej</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>367</v>
+      </c>
+      <c r="R56" t="n">
+        <v>523</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1234729561</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1234729561</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>바른몸PT센터</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>wlsrkfdl1@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1337-9711</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 20 3층 301호</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4frie</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>68</v>
+      </c>
+      <c r="R57" t="n">
+        <v>72</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2090651326</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2090651326</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>리조트휘트니스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>resort_5@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1438-0677</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ixpk</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>413</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>714</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1127</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>35524502</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35524502</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>피티스튜디오이룸 PT EROOM</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ptstudioeroom@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1361-7934</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 45 3층 303호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ptstudioeroom</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>32</v>
+      </c>
+      <c r="R59" t="n">
+        <v>78</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1164280530</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1164280530</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>더스튜디오엠 판교</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>acsmthestudiom@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로14번길 20 3층 더스튜디오엠 판교</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc8f76</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>704</v>
+      </c>
+      <c r="R60" t="n">
+        <v>709</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>34818222</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34818222</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>크레이지핏 PT</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>krazyfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1488-5883</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>535</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1437</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1972</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1628554288</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628554288</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>이상해GYM PT 판교역점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>isanghaegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1399-9644</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 지2층 B2086호</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w1cs1tt</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>124</v>
+      </c>
+      <c r="R62" t="n">
+        <v>190</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1053530808</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1053530808</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>맑음체육관 PT 판교역점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>malgum_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1444-1386</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 3층 305호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wt7dwa7</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>26</v>
+      </c>
+      <c r="R63" t="n">
+        <v>105</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1424547961</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1424547961</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>제로퍼스널트레이닝PT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>phh3014@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1341-5808</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 115 판오션타워 501호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41tad</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>10</v>
+      </c>
+      <c r="R64" t="n">
+        <v>15</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>21647284</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21647284</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>healthboygym78@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1402-1275</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>2535</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>322</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2857</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1835201778</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1835201778</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>열정PT 판교점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ptpassion@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1319-7157</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로255번길 9-22 우림W-CITY 지하117호</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ptpassion</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>209</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>154</v>
+      </c>
+      <c r="R66" t="n">
+        <v>363</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1614896755</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1614896755</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>바른몸 PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ottlottl@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1392-8244</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로3길 15 1층 101호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl2yvsw</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>5</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>2096956392</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2096956392</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>바로선운동센터 판교점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>coolksh11@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wve1811</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>180</v>
+      </c>
+      <c r="R68" t="n">
+        <v>202</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2015061102</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2015061102</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>머슬짐 PT 분당서현점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>musclegym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1436-9680</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로342번길 19 유성그린빌딩 6층</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/musclegym_</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>367</v>
+      </c>
+      <c r="R69" t="n">
+        <v>567</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1208748555</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1208748555</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>버핏그라운드 판교</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1329-4325</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://pt.butfitground.com/</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42raj</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>1766</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>249</v>
+      </c>
+      <c r="R70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1136752576</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1136752576</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>데스런 판교점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>deslun@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1412-6347</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>http://www.deslun.co.kr</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ty8f</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>365</v>
+      </c>
+      <c r="R71" t="n">
+        <v>385</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>31469573</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31469573</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>턴핏PT 판교운중점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>sungbin00@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>031-698-4246</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 131 803호, 804호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a9c1</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>68</v>
+      </c>
+      <c r="R72" t="n">
+        <v>104</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1457398870</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1457398870</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>153트레이닝</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>trainerps@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1361-0679</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로3길 36 202호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>19</v>
+      </c>
+      <c r="R73" t="n">
+        <v>20</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1932735845</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1932735845</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ACS 스트레칭 판교</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>cldud777725@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1389-4127</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 판교역푸르지오월드마크 상가1층 72호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.npsacs.com</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ijjd</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>2</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1136320574</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1136320574</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>버핏그라운드 판교벤처타운</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1315-3624</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.butfitground.com/</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>28</v>
+      </c>
+      <c r="R75" t="n">
+        <v>138</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2064425838</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2064425838</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>트친소</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>govlrhaehfdl@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1349-0679</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>85</v>
+      </c>
+      <c r="R76" t="n">
+        <v>85</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1911382745</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1911382745</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/판교_PT.xlsx
+++ b/naver-place-crawler/results_health/판교_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>원팀짐</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>oneteamgym-@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-702-2070</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 128 7층 701호</t>
+          <t>경기 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oneteamgym1</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>492</v>
+        <v>2540</v>
       </c>
       <c r="Q2" t="n">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="R2" t="n">
-        <v>781</v>
+        <v>2863</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1973455447</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973455447</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>원팀짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
+          <t>oneteamgym-@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>031-702-2070</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기 성남시 분당구 운중로 128 7층 701호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>https://www.instagram.com/oneteamgym1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl0ubx8</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>162</v>
+        <v>492</v>
       </c>
       <c r="Q3" t="n">
-        <v>143</v>
+        <v>289</v>
       </c>
       <c r="R3" t="n">
-        <v>305</v>
+        <v>781</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>1973455447</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/1973455447</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>레조나헬스랩PT 서판교점</t>
+          <t>리조트휘트니스 PT 판교점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>resonar_healthlab@naver.com</t>
+          <t>resort_5@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1411-1104</t>
+          <t>0507-1438-0677</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
+          <t>경기 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resonar_healthlab</t>
+          <t>https://www.instagram.com/resortfitness__pangyo/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,15 +797,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ixpk</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>56</v>
+        <v>412</v>
       </c>
       <c r="Q4" t="n">
-        <v>202</v>
+        <v>714</v>
       </c>
       <c r="R4" t="n">
-        <v>258</v>
+        <v>1126</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1644348689</t>
+          <t>35524502</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1644348689</t>
+          <t>https://m.place.naver.com/place/35524502</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>업투 휘트니스 분당판교점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>uptofitness-@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1343-8274</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기 성남시 분당구 동판교로 59 6층 601-605호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://blog.naver.com/uptofitness-</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ijhg</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2540</v>
+        <v>618</v>
       </c>
       <c r="Q5" t="n">
-        <v>323</v>
+        <v>291</v>
       </c>
       <c r="R5" t="n">
-        <v>2863</v>
+        <v>909</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1928497638</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1928497638</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리조트휘트니스 PT 판교점</t>
+          <t>데스런 판교점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>resort_5@naver.com</t>
+          <t>deslun@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1438-0677</t>
+          <t>0507-1412-6347</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+          <t>경기 성남시 분당구 판교역로2번길 38</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+          <t>http://www.deslun.co.kr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ty8f</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,14 +1017,14 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>390</v>
+      </c>
+      <c r="R6" t="n">
         <v>412</v>
       </c>
-      <c r="Q6" t="n">
-        <v>714</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1126</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1012,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>35524502</t>
+          <t>31469573</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35524502</t>
+          <t>https://m.place.naver.com/place/31469573</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1029,34 +1049,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>업투 휘트니스 분당판교점</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uptofitness-@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1343-8274</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+          <t>경기 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/uptofitness-</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1076,13 +1100,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42raj</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>618</v>
+        <v>1765</v>
       </c>
       <c r="Q7" t="n">
-        <v>291</v>
+        <v>250</v>
       </c>
       <c r="R7" t="n">
-        <v>909</v>
+        <v>2015</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1134,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1928497638</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928497638</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,34 +1156,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>데스런 판교점</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>deslun@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1412-6347</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.deslun.co.kr</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1193,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>141</v>
       </c>
       <c r="Q8" t="n">
-        <v>385</v>
+        <v>1437</v>
       </c>
       <c r="R8" t="n">
-        <v>407</v>
+        <v>1578</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>31469573</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31469573</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,38 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>베스트바디발란스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>wjdwktnso@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1402-7136</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://blog.naver.com/wjdwktnso</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1268,28 +1292,32 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc9u20</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1765</v>
+        <v>54</v>
       </c>
       <c r="Q9" t="n">
-        <v>250</v>
+        <v>107</v>
       </c>
       <c r="R9" t="n">
-        <v>2015</v>
+        <v>161</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>36428321</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/36428321</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>프로원핏 정자점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>betabros-@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1466-0213</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기 성남시 분당구 정자로 13 3층 310호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://blog.naver.com/betabros-</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1362,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wq9pona</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="Q10" t="n">
-        <v>1437</v>
+        <v>23</v>
       </c>
       <c r="R10" t="n">
-        <v>1578</v>
+        <v>50</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1322454491</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1322454491</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1407,55 +1439,35 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>버핏그라운드 PT 판교</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1417-1133</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1466,12 +1478,12 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1490,12 +1502,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2029680813</t>
+          <t>2600001</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
+          <t>https://m.place.naver.com/place/2600001</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1505,32 +1517,20 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>팀버핏 판교</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하3층 B3008</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/butfitground</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1561,17 +1561,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>331</v>
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1580,15 +1580,249 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1004612269</t>
+          <t>7167332</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1004612269</t>
+          <t>https://m.place.naver.com/place/7167332</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>7258722</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7258722</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>7142668</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7142668</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>7583905</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7583905</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/판교_PT.xlsx
+++ b/naver-place-crawler/results_health/판교_PT.xlsx
@@ -423,16 +423,16 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wi2wapb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 운중로 128 7층 701호</t>
+          <t>경기도 성남시 분당구 운중로 128 7층 701호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wl0ubx8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>리조트휘트니스 PT 판교점</t>
+          <t>구스짐 PT 판교점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>resort_5@naver.com</t>
+          <t>chlgudrn1@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1438-0677</t>
+          <t>0507-1465-9683</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+          <t>https://www.instagram.com/9s_gym_pangyo/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ixpk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>412</v>
+        <v>163</v>
       </c>
       <c r="Q4" t="n">
-        <v>714</v>
+        <v>143</v>
       </c>
       <c r="R4" t="n">
-        <v>1126</v>
+        <v>306</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>35524502</t>
+          <t>1088776551</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35524502</t>
+          <t>https://m.place.naver.com/place/1088776551</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>업투 휘트니스 분당판교점</t>
+          <t>리조트휘트니스 PT 판교점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uptofitness-@naver.com</t>
+          <t>resort_5@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1343-8274</t>
+          <t>0507-1438-0677</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 동판교로 59 6층 601-605호</t>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/uptofitness-</t>
+          <t>https://www.instagram.com/resortfitness__pangyo/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,19 +883,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ijhg</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>618</v>
+        <v>413</v>
       </c>
       <c r="Q5" t="n">
-        <v>291</v>
+        <v>714</v>
       </c>
       <c r="R5" t="n">
-        <v>909</v>
+        <v>1127</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1928497638</t>
+          <t>35524502</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928497638</t>
+          <t>https://m.place.naver.com/place/35524502</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 판교역로2번길 38</t>
+          <t>경기도 성남시 분당구 판교역로2번길 38</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ty8f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1020,10 +1000,10 @@
         <v>22</v>
       </c>
       <c r="Q6" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="R6" t="n">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1049,38 +1029,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>업투 휘트니스 분당판교점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>uptofitness-@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1343-8274</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://blog.naver.com/uptofitness-</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1100,17 +1076,13 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42raj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1119,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1765</v>
+        <v>619</v>
       </c>
       <c r="Q7" t="n">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="R7" t="n">
-        <v>2015</v>
+        <v>910</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1134,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1928497638</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1928497638</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1151,34 +1123,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1204,7 +1180,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>141</v>
+        <v>1765</v>
       </c>
       <c r="Q8" t="n">
-        <v>1437</v>
+        <v>250</v>
       </c>
       <c r="R8" t="n">
-        <v>1578</v>
+        <v>2015</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>베스트바디발란스</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wjdwktnso@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1402-7136</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjdwktnso</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1292,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc9u20</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,17 +1279,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="Q9" t="n">
-        <v>107</v>
+        <v>1437</v>
       </c>
       <c r="R9" t="n">
-        <v>161</v>
+        <v>1578</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36428321</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428321</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1348,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로원핏 정자점</t>
+          <t>베스트바디발란스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>betabros-@naver.com</t>
+          <t>wjdwktnso@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1466-0213</t>
+          <t>0507-1402-7136</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 정자로 13 3층 310호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/betabros-</t>
+          <t>https://blog.naver.com/wjdwktnso</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1390,14 +1362,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wq9pona</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,17 +1373,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="R10" t="n">
-        <v>50</v>
+        <v>161</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1322454491</t>
+          <t>36428321</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1322454491</t>
+          <t>https://m.place.naver.com/place/36428321</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/판교_PT.xlsx
+++ b/naver-place-crawler/results_health/판교_PT.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -1000,10 +1000,10 @@
         <v>22</v>
       </c>
       <c r="Q6" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="R6" t="n">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1320,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>베스트바디발란스</t>
+          <t>프로원핏 정자점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wjdwktnso@naver.com</t>
+          <t>betabros-@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1402-7136</t>
+          <t>0507-1466-0213</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
+          <t>경기도 성남시 분당구 정자로 13 3층 310호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjdwktnso</t>
+          <t>https://blog.naver.com/betabros-</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="Q10" t="n">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="R10" t="n">
-        <v>161</v>
+        <v>50</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>36428321</t>
+          <t>1322454491</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428321</t>
+          <t>https://m.place.naver.com/place/1322454491</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1407,25 +1407,41 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H GYM PT GT 판교2호점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1353-9408</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://hgym.imweb.me</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1435,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1451,17 +1467,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1470,12 +1486,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2600001</t>
+          <t>1850894755</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2600001</t>
+          <t>https://m.place.naver.com/place/1850894755</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1485,20 +1501,32 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>let_me_pt_official@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/let_me_pt_official</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1508,12 +1536,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1529,17 +1557,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1548,249 +1576,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>7167332</t>
+          <t>1049956503</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7167332</t>
+          <t>https://m.place.naver.com/place/1049956503</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>7258722</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7258722</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>7142668</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7142668</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>7583905</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7583905</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/판교_PT.xlsx
+++ b/naver-place-crawler/results_health/판교_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="41" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,20 +596,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -646,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -663,7 +667,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>oneteamgym-@naver.com</t>
+          <t>makefitness3@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -680,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oneteamgym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl0ubx8</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Q3" t="n">
         <v>289</v>
       </c>
       <c r="R3" t="n">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -752,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>리조트휘트니스 PT 판교점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
+          <t>resort_5@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1438-0677</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ixpk</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>163</v>
+        <v>413</v>
       </c>
       <c r="Q4" t="n">
-        <v>143</v>
+        <v>714</v>
       </c>
       <c r="R4" t="n">
-        <v>306</v>
+        <v>1127</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>35524502</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/35524502</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,34 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>리조트휘트니스 PT 판교점</t>
+          <t>데스런 판교점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>resort_5@naver.com</t>
+          <t>deslun@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1438-0677</t>
+          <t>0507-1412-6347</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+          <t>경기도 성남시 분당구 판교역로2번길 38</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+          <t>http://www.deslun.co.kr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ty8f</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>413</v>
+        <v>22</v>
       </c>
       <c r="Q5" t="n">
-        <v>714</v>
+        <v>399</v>
       </c>
       <c r="R5" t="n">
-        <v>1127</v>
+        <v>421</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>35524502</t>
+          <t>31469573</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35524502</t>
+          <t>https://m.place.naver.com/place/31469573</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -940,39 +956,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>데스런 판교점</t>
+          <t>업투 휘트니스 분당판교점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>deslun@naver.com</t>
+          <t>uptofitness-@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1412-6347</t>
+          <t>0507-1343-8274</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.deslun.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ijhg</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>619</v>
       </c>
       <c r="Q6" t="n">
-        <v>398</v>
+        <v>291</v>
       </c>
       <c r="R6" t="n">
-        <v>420</v>
+        <v>910</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1032,55 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>31469573</t>
+          <t>1928497638</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31469573</t>
+          <t>https://m.place.naver.com/place/1928497638</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>업투 휘트니스 분당판교점</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uptofitness-@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1343-8274</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/uptofitness-</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1076,13 +1100,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42raj</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>619</v>
+        <v>1765</v>
       </c>
       <c r="Q7" t="n">
-        <v>291</v>
+        <v>250</v>
       </c>
       <c r="R7" t="n">
-        <v>910</v>
+        <v>2015</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,55 +1134,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1928497638</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928497638</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>프로원핏 정자점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>pro1fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1466-0213</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 정자로 13 3층 310호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1164,23 +1188,27 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wq9pona</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1189,13 +1217,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1765</v>
+        <v>27</v>
       </c>
       <c r="Q8" t="n">
-        <v>250</v>
+        <v>23</v>
       </c>
       <c r="R8" t="n">
-        <v>2015</v>
+        <v>50</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,17 +1232,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1322454491</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1322454491</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1226,39 +1254,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>H GYM PT GT 판교2호점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>hgym9408@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1353-9408</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://hgym.imweb.me</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1268,10 +1296,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47alh</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>141</v>
+        <v>279</v>
       </c>
       <c r="Q9" t="n">
-        <v>1437</v>
+        <v>420</v>
       </c>
       <c r="R9" t="n">
-        <v>1578</v>
+        <v>699</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,17 +1330,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1850894755</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1850894755</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1320,29 +1352,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로원핏 정자점</t>
+          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>betabros-@naver.com</t>
+          <t>let_me_pt_official@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1466-0213</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자로 13 3층 310호</t>
+          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/betabros-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1352,20 +1380,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42m9n</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="R10" t="n">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,56 +1424,40 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1322454491</t>
+          <t>1049956503</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1322454491</t>
+          <t>https://m.place.naver.com/place/1049956503</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>H GYM PT GT 판교2호점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>hgym9408@naver.com</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1353-9408</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 233 302호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://hgym.imweb.me</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1451,7 +1467,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,17 +1483,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,47 +1502,35 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1850894755</t>
+          <t>2600001</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850894755</t>
+          <t>https://m.place.naver.com/place/2600001</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>let_me_pt_official@naver.com</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/let_me_pt_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1536,12 +1540,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1557,17 +1561,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1580,251 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1049956503</t>
+          <t>7167332</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049956503</t>
+          <t>https://m.place.naver.com/place/7167332</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>7258722</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7258722</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>7142668</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7142668</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>7583905</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7583905</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/판교_PT.xlsx
+++ b/naver-place-crawler/results_health/판교_PT.xlsx
@@ -421,18 +421,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="41" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,24 +596,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wi2wapb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -667,7 +663,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>makefitness3@naver.com</t>
+          <t>oneteamgym-@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -684,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/oneteamgym1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wl0ubx8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -782,7 +774,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/resortfitness__pangyo/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ixpk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -824,10 +812,10 @@
         <v>413</v>
       </c>
       <c r="Q4" t="n">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="R4" t="n">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ty8f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -922,10 +906,10 @@
         <v>22</v>
       </c>
       <c r="Q5" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="R5" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/uptofitness-</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,24 +972,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ijhg</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1100,14 +1080,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42raj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>O</t>
@@ -1156,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로원핏 정자점</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pro1fit@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1466-0213</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자로 13 3층 310호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1188,24 +1164,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wq9pona</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1217,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>1437</v>
       </c>
       <c r="R8" t="n">
-        <v>50</v>
+        <v>1578</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1322454491</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1322454491</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1254,39 +1226,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H GYM PT GT 판교2호점</t>
+          <t>베스트바디발란스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hgym9408@naver.com</t>
+          <t>wjdwktnso@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1353-9408</t>
+          <t>0507-1402-7136</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 233 302호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://hgym.imweb.me</t>
+          <t>https://blog.naver.com/wjdwktnso</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1296,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47alh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,17 +1279,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>279</v>
+        <v>54</v>
       </c>
       <c r="Q9" t="n">
-        <v>420</v>
+        <v>107</v>
       </c>
       <c r="R9" t="n">
-        <v>699</v>
+        <v>161</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1330,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1850894755</t>
+          <t>36428321</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850894755</t>
+          <t>https://m.place.naver.com/place/36428321</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1352,25 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
+          <t>프로원핏 정자점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>let_me_pt_official@naver.com</t>
+          <t>betabros-@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1466-0213</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
+          <t>경기도 성남시 분당구 정자로 13 3층 310호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/betabros-</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,24 +1352,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42m9n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1409,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="Q10" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="R10" t="n">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1049956503</t>
+          <t>1322454491</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049956503</t>
+          <t>https://m.place.naver.com/place/1322454491</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/판교_PT.xlsx
+++ b/naver-place-crawler/results_health/판교_PT.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="41" customWidth="1" min="7" max="7"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="Q2" t="n">
         <v>323</v>
       </c>
       <c r="R2" t="n">
-        <v>2863</v>
+        <v>2865</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -752,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>리조트휘트니스 PT 판교점</t>
+          <t>데스런 판교점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>resort_5@naver.com</t>
+          <t>deslun@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1438-0677</t>
+          <t>0507-1412-6347</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+          <t>경기도 성남시 분당구 판교역로2번길 38</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+          <t>http://www.deslun.co.kr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>413</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>715</v>
+        <v>411</v>
       </c>
       <c r="R4" t="n">
-        <v>1128</v>
+        <v>433</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>35524502</t>
+          <t>31469573</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35524502</t>
+          <t>https://m.place.naver.com/place/31469573</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>데스런 판교점</t>
+          <t>리조트휘트니스 PT 판교점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>deslun@naver.com</t>
+          <t>resort_5@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1412-6347</t>
+          <t>0507-1438-0677</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://www.deslun.co.kr</t>
+          <t>https://www.instagram.com/resortfitness__pangyo/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>22</v>
+        <v>413</v>
       </c>
       <c r="Q5" t="n">
-        <v>400</v>
+        <v>715</v>
       </c>
       <c r="R5" t="n">
-        <v>422</v>
+        <v>1128</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>31469573</t>
+          <t>35524502</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31469573</t>
+          <t>https://m.place.naver.com/place/35524502</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Q6" t="n">
         <v>291</v>
       </c>
       <c r="R6" t="n">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1029,48 +1029,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>H GYM PT GT 판교2호점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1353-9408</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://hgym.imweb.me</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1086,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1095,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1765</v>
+        <v>279</v>
       </c>
       <c r="Q7" t="n">
-        <v>250</v>
+        <v>420</v>
       </c>
       <c r="R7" t="n">
-        <v>2015</v>
+        <v>699</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1850894755</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1850894755</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1127,34 +1123,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,7 +1180,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>141</v>
+        <v>1765</v>
       </c>
       <c r="Q8" t="n">
-        <v>1437</v>
+        <v>250</v>
       </c>
       <c r="R8" t="n">
-        <v>1578</v>
+        <v>2015</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,34 +1226,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>베스트바디발란스</t>
+          <t>버핏그라운드 PT 판교</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wjdwktnso@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1402-7136</t>
+          <t>0507-1417-1133</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjdwktnso</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1274,22 +1278,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1302,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36428321</t>
+          <t>2029680813</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428321</t>
+          <t>https://m.place.naver.com/place/2029680813</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,29 +1324,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로원핏 정자점</t>
+          <t>베스트바디발란스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>betabros-@naver.com</t>
+          <t>wjdwktnso@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1466-0213</t>
+          <t>0507-1402-7136</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자로 13 3층 310호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/betabros-</t>
+          <t>https://blog.naver.com/wjdwktnso</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,17 +1377,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="R10" t="n">
-        <v>50</v>
+        <v>161</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1396,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1322454491</t>
+          <t>36428321</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1322454491</t>
+          <t>https://m.place.naver.com/place/36428321</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1407,20 +1411,36 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>프로원핏 정자점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>betabros-@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1466-0213</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 성남시 분당구 정자로 13 3층 310호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/betabros-</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1430,12 +1450,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1451,17 +1471,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1470,327 +1490,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2600001</t>
+          <t>1322454491</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2600001</t>
+          <t>https://m.place.naver.com/place/1322454491</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>7167332</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7167332</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>7258722</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7258722</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>7142668</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7142668</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>7583905</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7583905</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/판교_PT.xlsx
+++ b/naver-place-crawler/results_health/판교_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>블랙스미스짐 헬스PT 판교점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>emmaholic1@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1352-4388</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 판교역로 136 지하2층 비2147호, 비2148호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>http://blacksmithgym.kr/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41p6u</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2542</v>
+        <v>107</v>
       </c>
       <c r="Q2" t="n">
-        <v>323</v>
+        <v>194</v>
       </c>
       <c r="R2" t="n">
-        <v>2865</v>
+        <v>301</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1462760829</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1462760829</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>원팀짐</t>
+          <t>커스텀핏 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>oneteamgym-@naver.com</t>
+          <t>customfitpt@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>031-702-2070</t>
+          <t>031-8016-5677</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 128 7층 701호</t>
+          <t>경기도 성남시 분당구 운중로 123 마크시티 오렌지동 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oneteamgym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +715,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>493</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>289</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>782</v>
+        <v>5</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1973455447</t>
+          <t>35644006</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973455447</t>
+          <t>https://m.place.naver.com/place/35644006</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,39 +756,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>데스런 판교점</t>
+          <t>더스튜디오엠 판교</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>deslun@naver.com</t>
+          <t>acsmthestudiom@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1412-6347</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+          <t>경기도 성남시 분당구 판교역로14번길 20 3층 더스튜디오엠 판교</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.deslun.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -794,10 +794,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc8f76</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -805,17 +809,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="n">
-        <v>411</v>
+        <v>705</v>
       </c>
       <c r="R4" t="n">
-        <v>433</v>
+        <v>710</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>31469573</t>
+          <t>34818222</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31469573</t>
+          <t>https://m.place.naver.com/place/34818222</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>리조트휘트니스 PT 판교점</t>
+          <t>리,무브먼트</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>resort_5@naver.com</t>
+          <t>sujin6735@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1438-0677</t>
+          <t>0507-1310-5661</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +882,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -888,10 +892,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ag69</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>413</v>
+        <v>242</v>
       </c>
       <c r="Q5" t="n">
-        <v>715</v>
+        <v>246</v>
       </c>
       <c r="R5" t="n">
-        <v>1128</v>
+        <v>488</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +926,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>35524502</t>
+          <t>1149465061</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35524502</t>
+          <t>https://m.place.naver.com/place/1149465061</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,29 +948,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>업투 휘트니스 분당판교점</t>
+          <t>엑서사이언스짐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>uptofitness-@naver.com</t>
+          <t>exerscience@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1343-8274</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+          <t>경기도 성남시 분당구 판교역로 240 삼환하이펙스A동 B1층 B117-1호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/uptofitness-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,20 +976,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vur6</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -993,17 +1001,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>620</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>291</v>
+        <v>143</v>
       </c>
       <c r="R6" t="n">
-        <v>911</v>
+        <v>150</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1020,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1928497638</t>
+          <t>1746641680</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928497638</t>
+          <t>https://m.place.naver.com/place/1746641680</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1034,34 +1042,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H GYM PT GT 판교2호점</t>
+          <t>업투 휘트니스 분당판교점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hgym9408@naver.com</t>
+          <t>uptofitness-@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1353-9408</t>
+          <t>0507-1343-8274</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 233 302호</t>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://hgym.imweb.me</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,15 +1079,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ijhg</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>279</v>
+        <v>620</v>
       </c>
       <c r="Q7" t="n">
-        <v>420</v>
+        <v>291</v>
       </c>
       <c r="R7" t="n">
-        <v>699</v>
+        <v>911</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,55 +1118,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1850894755</t>
+          <t>1928497638</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850894755</t>
+          <t>https://m.place.naver.com/place/1928497638</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>바른몸 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>ottlottl@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1392-8244</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 판교공원로3길 15 1층 101호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1164,23 +1172,27 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl2yvsw</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1189,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1765</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>2015</v>
+        <v>6</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,17 +1216,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>2096956392</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/2096956392</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1226,48 +1238,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 판교</t>
+          <t>판교피트니스센터</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>towershift@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1417-1133</t>
+          <t>0507-1343-5171</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+          <t>경기도 성남시 분당구 판교로289번길 20 3층 판교피트니스센터</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1278,7 +1286,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1287,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,17 +1310,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2029680813</t>
+          <t>1874121479</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
+          <t>https://m.place.naver.com/place/1874121479</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1324,29 +1332,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>베스트바디발란스</t>
+          <t>헬스보이짐&amp;필라걸 수내점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wjdwktnso@naver.com</t>
+          <t>healthboy40@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1402-7136</t>
+          <t>0507-1380-2239</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjdwktnso</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1356,20 +1364,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4laa0</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1377,17 +1389,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>54</v>
+        <v>968</v>
       </c>
       <c r="Q10" t="n">
-        <v>107</v>
+        <v>737</v>
       </c>
       <c r="R10" t="n">
-        <v>161</v>
+        <v>1705</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,17 +1408,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>36428321</t>
+          <t>1973151166</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428321</t>
+          <t>https://m.place.naver.com/place/1973151166</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1418,29 +1430,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>프로원핏 정자점</t>
+          <t>포랩 이즈메디운동센터</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>betabros-@naver.com</t>
+          <t>for_lab2017@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1466-0213</t>
+          <t>0507-1432-1575</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자로 13 3층 310호</t>
+          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/betabros-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1450,20 +1462,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc1hom</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1475,32 +1491,6330 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>289</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>158</v>
+      </c>
+      <c r="R11" t="n">
+        <v>447</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>917204514</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/917204514</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>열정PT 판교점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ptpassion@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1319-7157</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로255번길 9-22 우림W-CITY 지하117호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5umoy</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>154</v>
+      </c>
+      <c r="R12" t="n">
+        <v>361</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1614896755</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1614896755</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>건강한 운동 연구소</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>brave082@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1347-2906</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로44번길 3-14 102호 건강한 운동 연구소</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>20</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1780907875</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1780907875</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>유앤바디PT 분당수내점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>unbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>031-714-4729</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 12 세인프라자 402호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4b6la</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>167</v>
+      </c>
+      <c r="R14" t="n">
+        <v>285</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1853394852</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1853394852</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>턴핏PT 판교운중점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sungbin00@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>031-698-4246</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 131 803호, 804호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a9c1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>68</v>
+      </c>
+      <c r="R15" t="n">
+        <v>104</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1457398870</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1457398870</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>라이프타임PT 판교대장점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>lifetimept@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1381-7696</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로8길 16 클라우드베이 5단지 상가 2층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_bmUkb</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>37</v>
+      </c>
+      <c r="R16" t="n">
+        <v>111</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1012341140</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1012341140</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>제로퍼스널트레이닝PT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>phh3014@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1341-5808</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 115 판오션타워 501호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41tad</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>10</v>
+      </c>
+      <c r="R17" t="n">
+        <v>15</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>21647284</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21647284</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>바디수</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>lovelygodus@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>070-8802-9000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로44번길 15 101호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>http://www.bodysoo.co.kr/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>11</v>
+      </c>
+      <c r="R18" t="n">
+        <v>16</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>32497004</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32497004</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>트친소</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>govlrhaehfdl@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1349-0679</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>85</v>
+      </c>
+      <c r="R19" t="n">
+        <v>85</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1911382745</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1911382745</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>복싱,권투장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>카운터복싱 판교대장점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>counterboxing13@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1365-8859</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로8길 8 303호, 304호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u3lu</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>210</v>
+      </c>
+      <c r="R20" t="n">
+        <v>215</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1889442444</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1889442444</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>바디센서리 판교점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>bodysensory@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1344-2096</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 41 프라임스퀘어 10층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4124s</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>292</v>
+      </c>
+      <c r="R21" t="n">
+        <v>338</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1786901360</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1786901360</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>핏불짐 판교점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>fitbullgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1430-9683</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2 3층 304호</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/fitbullgym</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>284</v>
+      </c>
+      <c r="R22" t="n">
+        <v>376</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>37814535</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37814535</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>스윕피티필라테스</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>songj1919@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 상가동 1층 105,106호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcc6zd5</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>102</v>
+      </c>
+      <c r="R23" t="n">
+        <v>119</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1734844856</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1734844856</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>피티스튜디오이룸 PT EROOM</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ptstudioeroom@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1361-7934</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 45 3층 303호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wuyghv5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>32</v>
+      </c>
+      <c r="R24" t="n">
+        <v>79</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1164280530</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1164280530</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>머슬짐 PT 분당서현점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>musclegym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1436-9680</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로342번길 19 유성그린빌딩 6층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wgye1u3</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>367</v>
+      </c>
+      <c r="R25" t="n">
+        <v>567</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1208748555</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1208748555</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>하이퀄짐 헬스PT 판교점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>highqualgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1364-9601</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 128 2층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w406tf</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>103</v>
+      </c>
+      <c r="R26" t="n">
+        <v>161</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1012638231</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1012638231</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>구스짐 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>chlgudrn1@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1465-9683</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyuehl2</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>143</v>
+      </c>
+      <c r="R27" t="n">
+        <v>307</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1088776551</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088776551</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>솔리드짐 PT 수내점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ppapers@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1420-7858</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tbft</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>652</v>
+      </c>
+      <c r="R28" t="n">
+        <v>797</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1205679892</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1205679892</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>스포애니 서현역점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>spoany22@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>031-706-8522</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40q6m</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>953</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2039</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2992</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>13025013</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13025013</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>크레이지핏 PT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>krazyfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1488-5883</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>538</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1438</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1976</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1628554288</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628554288</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PDC스포츠센터</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>spxkzjs12@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>031-8060-0377</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 242 판교디지털센터 A동 2층 PDC스포츠센터</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>19</v>
+      </c>
+      <c r="R31" t="n">
+        <v>71</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1057141943</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1057141943</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>파우즈더바디 이매점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>pausethebodytraining@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1425-7282</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 432 4층 1호</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pause_the_body_imae</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>9</v>
+      </c>
+      <c r="R32" t="n">
+        <v>71</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1577244696</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1577244696</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>데스런 판교점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>deslun@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1412-6347</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>http://www.deslun.co.kr</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ty8f</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>415</v>
+      </c>
+      <c r="R33" t="n">
+        <v>437</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>31469573</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31469573</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>바디브레인PT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>skemfisz1@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1329-8163</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로779번길 52 502호</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43v5l</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>80</v>
+      </c>
+      <c r="R34" t="n">
+        <v>166</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1075198509</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1075198509</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>버핏그라운드 PT 판교벤처타운</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1304-0676</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.butfitground.com/4steppt</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2030115135</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2030115135</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>휘트니스클럽S 수내점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>fitnessclubs12@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1311-1188</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 11 5층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49zvx</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>308</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>917</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1225</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1228787055</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1228787055</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>뱅핏 PT 판교운중점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>bangfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1345-4609</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 122 골드클래스 8층 801호, 802호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40lij</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>245</v>
+      </c>
+      <c r="R37" t="n">
+        <v>310</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1890400282</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1890400282</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>맑음체육관 PT 판교역점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>malgum_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1444-1386</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 3층 305호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wt7dwa7</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>26</v>
+      </c>
+      <c r="R38" t="n">
+        <v>105</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1424547961</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1424547961</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H GYM PT GT 판교2호점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1353-9408</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://hgym.imweb.me</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47alh</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>421</v>
+      </c>
+      <c r="R39" t="n">
+        <v>700</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1850894755</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850894755</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>캔들짐</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>tnghkd213@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1333-7650</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 판교푸르지오월드마크 제2-17호 캔들짐</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/Candlegymfitness</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>8</v>
+      </c>
+      <c r="R40" t="n">
+        <v>14</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1242676842</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1242676842</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>153트레이닝</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>trainerps@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1361-0679</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로3길 36 202호</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>19</v>
+      </c>
+      <c r="R41" t="n">
+        <v>20</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1932735845</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1932735845</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D gym PT 수내역점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>hyenggoo1@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1438-1374</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로200번길 34 205, 206호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40pej</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>367</v>
+      </c>
+      <c r="R42" t="n">
+        <v>523</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1234729561</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1234729561</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>뉴로스위칭 판교본점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>team_hero@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1403-9311</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1A 제2층 216호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>41</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>34896927</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34896927</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>리조트휘트니스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>resort_5@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1438-0677</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ixpk</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>413</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>715</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1128</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>35524502</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35524502</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H GYM PT 대장3호점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1329-9408</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로 84 304호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://hgym.co.kr</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4aih7</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>111</v>
+      </c>
+      <c r="R45" t="n">
+        <v>222</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1027491629</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1027491629</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>써트짐 PT</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>certgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1367-7665</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로214번길 8 207호(수내동, MS프라자)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dpxc</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>237</v>
+      </c>
+      <c r="R46" t="n">
+        <v>286</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1331332549</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1331332549</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>바른몸 재활PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>wise_body_care@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1491-9925</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 376 6층 605호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5uzxa</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>35</v>
+      </c>
+      <c r="R47" t="n">
+        <v>117</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1253283857</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1253283857</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>이상해GYM PT 판교역점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>isanghaegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1399-9644</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 지2층 B2086호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w1cs1tt</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>124</v>
+      </c>
+      <c r="R48" t="n">
+        <v>191</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1053530808</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1053530808</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>원프로짐PT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>onepro_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1304-9363</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로 164 훼미리프라자 402호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wd5irjz</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>36</v>
+      </c>
+      <c r="R49" t="n">
+        <v>50</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1663447864</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1663447864</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>실내골프연습장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>철인짐</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>chulingym@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1475-0968</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 141 우리은행 건물 9층 철인짐</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xjbr</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>12</v>
+      </c>
+      <c r="R50" t="n">
+        <v>20</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1883390700</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1883390700</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>healthboygym78@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1402-1275</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>2543</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>323</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2866</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1835201778</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1835201778</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>베러댄 휘트니스 분당야탑점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>56zqrwcwsv@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1438-9698</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o2xj</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2093</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2475</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1013682807</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1013682807</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>H GYM PT GT 운중점</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1344-9408</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로188번길 8 1층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://hgym.co.kr</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gmmz</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>145</v>
+      </c>
+      <c r="R53" t="n">
+        <v>230</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1970444039</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1970444039</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>바로선운동센터 판교점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>coolksh11@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wve1811</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>187</v>
+      </c>
+      <c r="R54" t="n">
+        <v>209</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2015061102</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2015061102</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>좋은습관PTSTUDIO 판교운중</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>goodhabitpg@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1480-0677</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 142 6층</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wyz9</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>29</v>
+      </c>
+      <c r="R55" t="n">
+        <v>92</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1070284726</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1070284726</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>비아핏</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>viafit@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1379-7507</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로7길 15-2 지하1층,지상1층</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w37pnp4</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>24</v>
+      </c>
+      <c r="R56" t="n">
+        <v>50</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1772663783</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1772663783</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>제로업PT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>linefit91@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>031-623-2775</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 느티로 16 7층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>772</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>723</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1495</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1975822360</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1975822360</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>커스텀PT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>custom_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1485-0376</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로779번길 48 3층 304호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4074g</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>26</v>
+      </c>
+      <c r="R58" t="n">
+        <v>186</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1204743611</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1204743611</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>여성전용 비조 필라PT 자이로토닉</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>viyulgallery@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>themosttimes@tmt.co.kr</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 132</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.themosttimes.co.kr/43811</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4642d</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>50</v>
+      </c>
+      <c r="R59" t="n">
+        <v>179</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1600591794</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1600591794</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>바른몸PT센터</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>wlsrkfdl1@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1337-9711</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 20 3층 301호</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4frie</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>70</v>
+      </c>
+      <c r="R60" t="n">
+        <v>75</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>2090651326</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2090651326</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>피티세븐 퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>body2balance@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1400-9428</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>http://www.pts7.com</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4bej5</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>302</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>290</v>
+      </c>
+      <c r="R61" t="n">
+        <v>592</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>13093618</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13093618</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>halogym02@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1315-8840</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfevb4</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>663</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>933</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1596</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1806695299</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1806695299</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ACS 스트레칭 판교</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>cldud777725@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1389-4127</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 판교역푸르지오월드마크 상가1층 72호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.npsacs.com</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ijjd</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1136320574</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1136320574</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>핏앤클래시 PT</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>fitclassy22@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1325-5251</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로 154 낙생빌딩 201호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitclassy22</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>22</v>
+      </c>
+      <c r="R64" t="n">
+        <v>65</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1283224823</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1283224823</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>스윗바디</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>superfly3@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>031-701-4327</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로2번길 36 1층 스윗바디</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5whn9</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>19</v>
+      </c>
+      <c r="R65" t="n">
+        <v>82</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>20364482</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20364482</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>레조나헬스랩PT 서판교점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>resonar_healthlab@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1411-1104</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/resonar_healthlab</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>202</v>
+      </c>
+      <c r="R66" t="n">
+        <v>258</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1644348689</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1644348689</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>린바디핏 PT 판교본점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>leanbodyfitv2@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1302-8312</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 670 지하113호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3fqoyd</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>108</v>
+      </c>
+      <c r="R67" t="n">
+        <v>243</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1699238533</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1699238533</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>R31 필라테스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>r31functional@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1489-0374</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 58 나이스프라자 4층 402호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/r31functional</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>24</v>
+      </c>
+      <c r="R68" t="n">
+        <v>102</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1262189356</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1262189356</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>어반피트</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>urbanfit_@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1357-0997</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 128 601,602호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44gs9</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q69" t="n">
         <v>27</v>
       </c>
-      <c r="Q11" t="n">
-        <v>23</v>
-      </c>
-      <c r="R11" t="n">
-        <v>50</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1322454491</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1322454491</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+      <c r="R69" t="n">
+        <v>60</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1138293980</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1138293980</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>근육연구소</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>musclelab_9609@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1492-9193</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 109 A동 B212호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>172</v>
+      </c>
+      <c r="R70" t="n">
+        <v>177</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1655228047</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1655228047</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>버핏그라운드 PT 판교</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1417-1133</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.butfitground.com/4steppt</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>2029680813</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2029680813</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>버핏그라운드 판교</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1329-4325</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://pt.butfitground.com/</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42raj</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1765</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>250</v>
+      </c>
+      <c r="R72" t="n">
+        <v>2015</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1136752576</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1136752576</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>버핏그라운드 판교벤처타운</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1315-3624</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.butfitground.com/</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzq100p</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>29</v>
+      </c>
+      <c r="R73" t="n">
+        <v>140</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2064425838</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2064425838</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>에너지플로우짐</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>exerscience@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1346-9129</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B126-1호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://energyflowlab.my.canva.site</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>38</v>
+      </c>
+      <c r="R74" t="n">
+        <v>39</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1846760075</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1846760075</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>유밸런스</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>moveez@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1496-8969</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 140 203호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xvy6</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>103</v>
+      </c>
+      <c r="R75" t="n">
+        <v>138</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1069284280</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1069284280</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>팀제이맥스 피티 서현점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>linefit91@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>031-702-8296</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>910</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>548</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1458</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1639683746</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1639683746</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/판교_PT.xlsx
+++ b/naver-place-crawler/results_health/판교_PT.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>블랙스미스짐 헬스PT 판교점</t>
+          <t>트친소</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>emmaholic1@naver.com</t>
+          <t>govlrhaehfdl@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1352-4388</t>
+          <t>0507-1349-0679</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 지하2층 비2147호, 비2148호</t>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://blacksmithgym.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,32 +606,28 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w41p6u</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="R2" t="n">
-        <v>301</v>
+        <v>85</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1462760829</t>
+          <t>1911382745</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1462760829</t>
+          <t>https://m.place.naver.com/place/1911382745</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,29 +653,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>커스텀핏 PT</t>
+          <t>리,무브먼트</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>customfitpt@naver.com</t>
+          <t>sujin6735@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>031-8016-5677</t>
+          <t>0507-1310-5661</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 123 마크시티 오렌지동 3층</t>
+          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ag69</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,17 +715,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>242</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>246</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>488</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>35644006</t>
+          <t>1149465061</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35644006</t>
+          <t>https://m.place.naver.com/place/1149465061</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,25 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더스튜디오엠 판교</t>
+          <t>핏불짐 판교점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>acsmthestudiom@naver.com</t>
+          <t>fitbullgym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1430-9683</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로14번길 20 3층 더스튜디오엠 판교</t>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2 3층 304호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://linktr.ee/fitbullgym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,12 +788,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -799,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc8f76</t>
+          <t>https://talk.naver.com/ct/w4eqla</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -809,17 +813,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="Q4" t="n">
-        <v>705</v>
+        <v>284</v>
       </c>
       <c r="R4" t="n">
-        <v>710</v>
+        <v>376</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>34818222</t>
+          <t>37814535</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34818222</t>
+          <t>https://m.place.naver.com/place/37814535</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,24 +854,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>리,무브먼트</t>
+          <t>더스튜디오엠 판교</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sujin6735@naver.com</t>
+          <t>acsmthestudiom@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1310-5661</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
+          <t>경기도 성남시 분당구 판교역로14번길 20 3층 더스튜디오엠 판교</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ag69</t>
+          <t>https://talk.naver.com/ct/wc8f76</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>242</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>246</v>
+        <v>705</v>
       </c>
       <c r="R5" t="n">
-        <v>488</v>
+        <v>710</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1149465061</t>
+          <t>34818222</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1149465061</t>
+          <t>https://m.place.naver.com/place/34818222</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -948,20 +948,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>엑서사이언스짐</t>
+          <t>유밸런스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>exerscience@naver.com</t>
+          <t>moveez@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1496-8969</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 240 삼환하이펙스A동 B1층 B117-1호</t>
+          <t>경기도 성남시 분당구 운중로 140 203호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -991,7 +995,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vur6</t>
+          <t>https://talk.naver.com/ct/w5xvy6</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1001,17 +1005,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="n">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="R6" t="n">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1746641680</t>
+          <t>1069284280</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1746641680</t>
+          <t>https://m.place.naver.com/place/1069284280</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1042,24 +1046,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>업투 휘트니스 분당판교점</t>
+          <t>구스짐 PT 판교점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uptofitness-@naver.com</t>
+          <t>chlgudrn1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1343-8274</t>
+          <t>0507-1465-9683</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1089,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ijhg</t>
+          <t>https://talk.naver.com/ct/wyuehl2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1103,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>620</v>
+        <v>165</v>
       </c>
       <c r="Q7" t="n">
-        <v>291</v>
+        <v>143</v>
       </c>
       <c r="R7" t="n">
-        <v>911</v>
+        <v>308</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1928497638</t>
+          <t>1088776551</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928497638</t>
+          <t>https://m.place.naver.com/place/1088776551</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1135,29 +1139,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>바른몸 PT&amp;필라테스</t>
+          <t>원프로짐PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ottlottl@naver.com</t>
+          <t>onepro_gym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1392-8244</t>
+          <t>0507-1304-9363</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로3길 15 1층 101호</t>
+          <t>경기도 성남시 분당구 서판교로 164 훼미리프라자 402호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1187,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wl2yvsw</t>
+          <t>https://talk.naver.com/ct/wd5irjz</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2096956392</t>
+          <t>1663447864</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2096956392</t>
+          <t>https://m.place.naver.com/place/1663447864</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1238,24 +1242,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>판교피트니스센터</t>
+          <t>써트짐 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>towershift@naver.com</t>
+          <t>certgym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1343-5171</t>
+          <t>0507-1367-7665</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로289번길 20 3층 판교피트니스센터</t>
+          <t>경기도 성남시 분당구 황새울로214번길 8 207호(수내동, MS프라자)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1280,10 +1284,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dpxc</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1295,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>237</v>
       </c>
       <c r="R9" t="n">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1874121479</t>
+          <t>1331332549</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874121479</t>
+          <t>https://m.place.naver.com/place/1331332549</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1332,59 +1340,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸 수내점</t>
+          <t>버핏그라운드 PT 판교벤처타운</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>healthboy40@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1380-2239</t>
+          <t>0507-1304-0676</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
+          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4laa0</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1393,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>968</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>737</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1705</v>
+        <v>2</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1973151166</t>
+          <t>2030115135</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973151166</t>
+          <t>https://m.place.naver.com/place/2030115135</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1430,24 +1438,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>포랩 이즈메디운동센터</t>
+          <t>크레이지핏 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>for_lab2017@naver.com</t>
+          <t>krazyfit@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1432-1575</t>
+          <t>0507-1488-5883</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
+          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1477,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc1hom</t>
+          <t>https://talk.naver.com/ct/w44lbo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1491,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>289</v>
+        <v>539</v>
       </c>
       <c r="Q11" t="n">
-        <v>158</v>
+        <v>1438</v>
       </c>
       <c r="R11" t="n">
-        <v>447</v>
+        <v>1977</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>917204514</t>
+          <t>1628554288</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/917204514</t>
+          <t>https://m.place.naver.com/place/1628554288</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1528,24 +1536,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>열정PT 판교점</t>
+          <t>스윗바디</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ptpassion@naver.com</t>
+          <t>superfly3@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1319-7157</t>
+          <t>031-701-4327</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로255번길 9-22 우림W-CITY 지하117호</t>
+          <t>경기도 성남시 분당구 판교역로2번길 36 1층 스윗바디</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1575,7 +1583,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5umoy</t>
+          <t>https://talk.naver.com/ct/w5whn9</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1589,13 +1597,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>207</v>
+        <v>63</v>
       </c>
       <c r="Q12" t="n">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="R12" t="n">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1604,12 +1612,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1614896755</t>
+          <t>20364482</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1614896755</t>
+          <t>https://m.place.naver.com/place/20364482</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1626,24 +1634,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>건강한 운동 연구소</t>
+          <t>린바디핏 PT 판교본점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>brave082@naver.com</t>
+          <t>leanbodyfitv2@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1347-2906</t>
+          <t>0507-1302-8312</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 3-14 102호 건강한 운동 연구소</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 지하113호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1668,13 +1676,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3fqoyd</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1683,13 +1695,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="R13" t="n">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1698,12 +1710,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1780907875</t>
+          <t>1699238533</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1780907875</t>
+          <t>https://m.place.naver.com/place/1699238533</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1720,24 +1732,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>유앤바디PT 분당수내점</t>
+          <t>건강한 운동 연구소</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>unbody@naver.com</t>
+          <t>brave082@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>031-714-4729</t>
+          <t>0507-1347-2906</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 12 세인프라자 402호</t>
+          <t>경기도 성남시 분당구 서판교로44번길 3-14 102호 건강한 운동 연구소</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1762,14 +1774,10 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4b6la</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>X</t>
@@ -1777,17 +1785,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>167</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1796,12 +1804,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1853394852</t>
+          <t>1780907875</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853394852</t>
+          <t>https://m.place.naver.com/place/1780907875</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1818,24 +1826,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>턴핏PT 판교운중점</t>
+          <t>포랩 이즈메디운동센터</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sungbin00@naver.com</t>
+          <t>for_lab2017@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>031-698-4246</t>
+          <t>0507-1432-1575</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 131 803호, 804호</t>
+          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1865,7 +1873,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4a9c1</t>
+          <t>https://talk.naver.com/ct/wc1hom</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1879,13 +1887,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>36</v>
+        <v>289</v>
       </c>
       <c r="Q15" t="n">
-        <v>68</v>
+        <v>158</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>447</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1894,12 +1902,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1457398870</t>
+          <t>917204514</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1457398870</t>
+          <t>https://m.place.naver.com/place/917204514</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1911,44 +1919,44 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>라이프타임PT 판교대장점</t>
+          <t>R31 필라테스 PT 판교점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>lifetimept@naver.com</t>
+          <t>r31functional@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1381-7696</t>
+          <t>0507-1489-0374</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로8길 16 클라우드베이 5단지 상가 2층</t>
+          <t>경기도 성남시 분당구 동판교로 58 나이스프라자 4층 402호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_bmUkb</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1958,13 +1966,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w454nh</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1973,13 +1985,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="Q16" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="R16" t="n">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1988,12 +2000,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1012341140</t>
+          <t>1262189356</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1012341140</t>
+          <t>https://m.place.naver.com/place/1262189356</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2005,29 +2017,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>제로퍼스널트레이닝PT</t>
+          <t>스포애니 서현역점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>phh3014@naver.com</t>
+          <t>spoany22@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1341-5808</t>
+          <t>031-706-8522</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 115 판오션타워 501호</t>
+          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2057,7 +2069,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w41tad</t>
+          <t>https://talk.naver.com/ct/w40q6m</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2071,13 +2083,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>953</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>2039</v>
       </c>
       <c r="R17" t="n">
-        <v>15</v>
+        <v>2992</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2086,12 +2098,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>21647284</t>
+          <t>13025013</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21647284</t>
+          <t>https://m.place.naver.com/place/13025013</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2108,29 +2120,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>바디수</t>
+          <t>바디브레인PT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>lovelygodus@naver.com</t>
+          <t>skemfisz1@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>070-8802-9000</t>
+          <t>0507-1329-8163</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 15 101호</t>
+          <t>경기도 성남시 분당구 성남대로779번길 52 502호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://www.bodysoo.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2140,20 +2152,24 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43v5l</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>X</t>
@@ -2165,13 +2181,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="R18" t="n">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2180,12 +2196,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>32497004</t>
+          <t>1075198509</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32497004</t>
+          <t>https://m.place.naver.com/place/1075198509</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2202,24 +2218,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>트친소</t>
+          <t>로이핏1인PT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>govlrhaehfdl@naver.com</t>
+          <t>lyrdyd11@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1349-0679</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 9 4층</t>
+          <t>경기도 성남시 분당구 판교대장로6길 10 4층 ROYFIT STUDIO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2244,28 +2256,32 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h728</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q19" t="n">
-        <v>85</v>
+        <v>532</v>
       </c>
       <c r="R19" t="n">
-        <v>85</v>
+        <v>561</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2274,12 +2290,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1911382745</t>
+          <t>1191780262</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1911382745</t>
+          <t>https://m.place.naver.com/place/1191780262</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2291,49 +2307,53 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>카운터복싱 판교대장점</t>
+          <t>버핏그라운드 판교벤처타운</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>counterboxing13@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1365-8859</t>
+          <t>0507-1315-3624</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로8길 8 303호, 304호</t>
+          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.butfitground.com/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2343,27 +2363,27 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5u3lu</t>
+          <t>https://talk.naver.com/ct/wzq100p</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>111</v>
       </c>
       <c r="Q20" t="n">
-        <v>210</v>
+        <v>29</v>
       </c>
       <c r="R20" t="n">
-        <v>215</v>
+        <v>140</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2372,12 +2392,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1889442444</t>
+          <t>2064425838</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1889442444</t>
+          <t>https://m.place.naver.com/place/2064425838</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2394,24 +2414,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>바디센서리 판교점 헬스PT</t>
+          <t>하이퀄짐 헬스PT 판교점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>bodysensory@naver.com</t>
+          <t>highqualgym@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1344-2096</t>
+          <t>0507-1364-9601</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 41 프라임스퀘어 10층</t>
+          <t>경기도 성남시 분당구 운중로 128 2층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2441,7 +2461,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4124s</t>
+          <t>https://talk.naver.com/ct/w406tf</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2455,13 +2475,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="Q21" t="n">
-        <v>292</v>
+        <v>103</v>
       </c>
       <c r="R21" t="n">
-        <v>338</v>
+        <v>161</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2470,12 +2490,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1786901360</t>
+          <t>1012638231</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1786901360</t>
+          <t>https://m.place.naver.com/place/1012638231</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2492,29 +2512,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>핏불짐 판교점</t>
+          <t>맑음체육관 PT 판교역점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>fitbullgym@naver.com</t>
+          <t>malgum_fitness@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1430-9683</t>
+          <t>0507-1444-1386</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2 3층 304호</t>
+          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 3층 305호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://linktr.ee/fitbullgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2524,20 +2544,24 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wt7dwa7</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>X</t>
@@ -2549,13 +2573,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="Q22" t="n">
-        <v>284</v>
+        <v>26</v>
       </c>
       <c r="R22" t="n">
-        <v>376</v>
+        <v>105</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2564,12 +2588,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>37814535</t>
+          <t>1424547961</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37814535</t>
+          <t>https://m.place.naver.com/place/1424547961</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2581,25 +2605,29 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>스윕피티필라테스</t>
+          <t>캔들짐</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>songj1919@naver.com</t>
+          <t>tnghkd213@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1333-7650</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 상가동 1층 105,106호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 판교푸르지오월드마크 제2-17호 캔들짐</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2629,7 +2657,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcc6zd5</t>
+          <t>https://talk.naver.com/ct/w4bjuf</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2643,13 +2671,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Q23" t="n">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2658,12 +2686,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1734844856</t>
+          <t>1242676842</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1734844856</t>
+          <t>https://m.place.naver.com/place/1242676842</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2675,29 +2703,29 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>피티스튜디오이룸 PT EROOM</t>
+          <t>바른몸 재활PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ptstudioeroom@naver.com</t>
+          <t>wise_body_care@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1361-7934</t>
+          <t>0507-1491-9925</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 45 3층 303호</t>
+          <t>경기도 성남시 분당구 판교로 376 6층 605호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2727,12 +2755,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wuyghv5</t>
+          <t>https://talk.naver.com/ct/w5uzxa</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2741,13 +2769,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R24" t="n">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2756,12 +2784,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1164280530</t>
+          <t>1253283857</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1164280530</t>
+          <t>https://m.place.naver.com/place/1253283857</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2778,24 +2806,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>머슬짐 PT 분당서현점</t>
+          <t>팀제이맥스 피티 서현점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>musclegym_@naver.com</t>
+          <t>linefit91@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1436-9680</t>
+          <t>031-702-8296</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로342번길 19 유성그린빌딩 6층</t>
+          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2820,14 +2848,10 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wgye1u3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>X</t>
@@ -2839,13 +2863,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>200</v>
+        <v>910</v>
       </c>
       <c r="Q25" t="n">
-        <v>367</v>
+        <v>548</v>
       </c>
       <c r="R25" t="n">
-        <v>567</v>
+        <v>1458</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2854,12 +2878,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1208748555</t>
+          <t>1639683746</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1208748555</t>
+          <t>https://m.place.naver.com/place/1639683746</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2876,24 +2900,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>하이퀄짐 헬스PT 판교점</t>
+          <t>파우즈더바디 이매점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>highqualgym@naver.com</t>
+          <t>pausethebodytraining@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1364-9601</t>
+          <t>0507-1425-7282</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 128 2층</t>
+          <t>경기도 성남시 분당구 판교로 432 4층 1호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2918,14 +2942,10 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w406tf</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>X</t>
@@ -2937,13 +2957,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="Q26" t="n">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="R26" t="n">
-        <v>161</v>
+        <v>71</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2952,12 +2972,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1012638231</t>
+          <t>1577244696</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1012638231</t>
+          <t>https://m.place.naver.com/place/1577244696</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2969,34 +2989,38 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3006,12 +3030,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3021,12 +3045,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wyuehl2</t>
+          <t>https://talk.naver.com/ct/w42raj</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3035,13 +3059,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>164</v>
+        <v>1766</v>
       </c>
       <c r="Q27" t="n">
-        <v>143</v>
+        <v>250</v>
       </c>
       <c r="R27" t="n">
-        <v>307</v>
+        <v>2016</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3050,12 +3074,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3067,29 +3091,29 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>솔리드짐 PT 수내점</t>
+          <t>바른몸 PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ppapers@naver.com</t>
+          <t>ottlottl@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1420-7858</t>
+          <t>0507-1392-8244</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
+          <t>경기도 성남시 분당구 판교공원로3길 15 1층 101호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3119,7 +3143,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5tbft</t>
+          <t>https://talk.naver.com/ct/wl2yvsw</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3133,13 +3157,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>145</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>652</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>797</v>
+        <v>6</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3148,12 +3172,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1205679892</t>
+          <t>2096956392</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1205679892</t>
+          <t>https://m.place.naver.com/place/2096956392</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3165,29 +3189,29 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>스포애니 서현역점</t>
+          <t>열정PT 판교점</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>spoany22@naver.com</t>
+          <t>ptpassion@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>031-706-8522</t>
+          <t>0507-1319-7157</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
+          <t>경기도 성남시 분당구 판교로255번길 9-22 우림W-CITY 지하117호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3217,7 +3241,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40q6m</t>
+          <t>https://talk.naver.com/ct/w5umoy</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3231,13 +3255,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>953</v>
+        <v>207</v>
       </c>
       <c r="Q29" t="n">
-        <v>2039</v>
+        <v>154</v>
       </c>
       <c r="R29" t="n">
-        <v>2992</v>
+        <v>361</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3246,12 +3270,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>13025013</t>
+          <t>1614896755</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13025013</t>
+          <t>https://m.place.naver.com/place/1614896755</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3268,34 +3292,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>크레이지핏 PT</t>
+          <t>비아핏</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>krazyfit@naver.com</t>
+          <t>viafit@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1488-5883</t>
+          <t>0507-1379-7507</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
+          <t>경기도 성남시 분당구 판교대장로7길 15-2 지하1층,지상1층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3305,18 +3329,22 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w37pnp4</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3325,13 +3353,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>538</v>
+        <v>26</v>
       </c>
       <c r="Q30" t="n">
-        <v>1438</v>
+        <v>24</v>
       </c>
       <c r="R30" t="n">
-        <v>1976</v>
+        <v>50</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3340,12 +3368,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1628554288</t>
+          <t>1772663783</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628554288</t>
+          <t>https://m.place.naver.com/place/1772663783</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3357,29 +3385,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PDC스포츠센터</t>
+          <t>솔리드짐 PT 수내점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>spxkzjs12@naver.com</t>
+          <t>ppapers@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>031-8060-0377</t>
+          <t>0507-1420-7858</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 242 판교디지털센터 A동 2층 PDC스포츠센터</t>
+          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3404,10 +3432,14 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tbft</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>X</t>
@@ -3415,17 +3447,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>652</v>
       </c>
       <c r="R31" t="n">
-        <v>71</v>
+        <v>797</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3434,12 +3466,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1057141943</t>
+          <t>1205679892</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057141943</t>
+          <t>https://m.place.naver.com/place/1205679892</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3456,29 +3488,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>파우즈더바디 이매점</t>
+          <t>커스텀PT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>pausethebodytraining@naver.com</t>
+          <t>custom_pt@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1425-7282</t>
+          <t>0507-1485-0376</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 432 4층 1호</t>
+          <t>경기도 성남시 분당구 성남대로779번길 48 3층 304호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pause_the_body_imae</t>
+          <t>https://blog.naver.com/custom_pt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3493,7 +3525,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3513,13 +3545,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>62</v>
+        <v>160</v>
       </c>
       <c r="Q32" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="R32" t="n">
-        <v>71</v>
+        <v>186</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3528,12 +3560,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1577244696</t>
+          <t>1204743611</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1577244696</t>
+          <t>https://m.place.naver.com/place/1204743611</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3550,39 +3582,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>데스런 판교점</t>
+          <t>제로업PT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>deslun@naver.com</t>
+          <t>linefit91@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1412-6347</t>
+          <t>031-623-2775</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+          <t>경기도 성남시 분당구 느티로 16 7층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://www.deslun.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3592,14 +3624,10 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ty8f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>X</t>
@@ -3611,13 +3639,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>22</v>
+        <v>775</v>
       </c>
       <c r="Q33" t="n">
-        <v>415</v>
+        <v>730</v>
       </c>
       <c r="R33" t="n">
-        <v>437</v>
+        <v>1505</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3626,12 +3654,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>31469573</t>
+          <t>1975822360</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31469573</t>
+          <t>https://m.place.naver.com/place/1975822360</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3648,24 +3676,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>바디브레인PT</t>
+          <t>이상해GYM PT 판교역점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>skemfisz1@naver.com</t>
+          <t>isanghaegym@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1329-8163</t>
+          <t>0507-1399-9644</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로779번길 52 502호</t>
+          <t>경기도 성남시 분당구 판교역로 136 지2층 B2086호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3695,7 +3723,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w43v5l</t>
+          <t>https://talk.naver.com/ct/w1cs1tt</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3709,13 +3737,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="Q34" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="R34" t="n">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3724,12 +3752,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1075198509</t>
+          <t>1053530808</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1075198509</t>
+          <t>https://m.place.naver.com/place/1053530808</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3746,33 +3774,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 판교벤처타운</t>
+          <t>H GYM PT GT 운중점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1304-0676</t>
+          <t>0507-1344-9408</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
+          <t>경기도 성남시 분당구 운중로188번길 8 1층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://hgym.co.kr</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3782,7 +3806,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3792,13 +3816,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gmmz</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3807,13 +3835,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>230</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3822,12 +3850,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2030115135</t>
+          <t>1970444039</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2030115135</t>
+          <t>https://m.place.naver.com/place/1970444039</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3844,24 +3872,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>휘트니스클럽S 수내점</t>
+          <t>바디센서리 판교점 헬스PT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>fitnessclubs12@naver.com</t>
+          <t>bodysensory@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1311-1188</t>
+          <t>0507-1344-2096</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 11 5층</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 41 프라임스퀘어 10층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3891,7 +3919,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49zvx</t>
+          <t>https://talk.naver.com/ct/w4124s</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3905,13 +3933,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>308</v>
+        <v>46</v>
       </c>
       <c r="Q36" t="n">
-        <v>917</v>
+        <v>292</v>
       </c>
       <c r="R36" t="n">
-        <v>1225</v>
+        <v>338</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3920,12 +3948,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1228787055</t>
+          <t>1786901360</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228787055</t>
+          <t>https://m.place.naver.com/place/1786901360</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3937,39 +3965,39 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>뱅핏 PT 판교운중점</t>
+          <t>ACS 스트레칭 판교</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>bangfit@naver.com</t>
+          <t>cldud777725@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1345-4609</t>
+          <t>0507-1389-4127</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 122 골드클래스 8층 801호, 802호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 판교역푸르지오월드마크 상가1층 72호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.npsacs.com</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3979,7 +4007,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3989,12 +4017,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40lij</t>
+          <t>https://talk.naver.com/ct/w5ijjd</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4003,13 +4031,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="Q37" t="n">
-        <v>245</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>310</v>
+        <v>7</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -4018,12 +4046,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1890400282</t>
+          <t>1136320574</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1890400282</t>
+          <t>https://m.place.naver.com/place/1136320574</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4040,24 +4068,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>맑음체육관 PT 판교역점</t>
+          <t>레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>malgum_fitness@naver.com</t>
+          <t>resonar_healthlab@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1444-1386</t>
+          <t>0507-1411-1104</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 3층 305호</t>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4087,7 +4115,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wt7dwa7</t>
+          <t>https://talk.naver.com/ct/w42t22</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4101,13 +4129,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="Q38" t="n">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="R38" t="n">
-        <v>105</v>
+        <v>258</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4116,12 +4144,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1424547961</t>
+          <t>1644348689</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1424547961</t>
+          <t>https://m.place.naver.com/place/1644348689</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4138,34 +4166,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H GYM PT GT 판교2호점</t>
+          <t>D gym PT 수내역점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>hgym9408@naver.com</t>
+          <t>hyenggoo1@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1353-9408</t>
+          <t>0507-1438-1374</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 233 302호</t>
+          <t>경기도 성남시 분당구 황새울로200번길 34 205, 206호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://hgym.imweb.me</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4175,7 +4203,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4185,7 +4213,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w47alh</t>
+          <t>https://talk.naver.com/ct/w40pej</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4199,13 +4227,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>279</v>
+        <v>156</v>
       </c>
       <c r="Q39" t="n">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="R39" t="n">
-        <v>700</v>
+        <v>523</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4214,12 +4242,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1850894755</t>
+          <t>1234729561</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850894755</t>
+          <t>https://m.place.naver.com/place/1234729561</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4236,29 +4264,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>캔들짐</t>
+          <t>핏앤클래시 PT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>tnghkd213@naver.com</t>
+          <t>fitclassy22@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1333-7650</t>
+          <t>0507-1325-5251</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 판교푸르지오월드마크 제2-17호 캔들짐</t>
+          <t>경기도 성남시 분당구 서판교로 154 낙생빌딩 201호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/Candlegymfitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4268,7 +4296,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4278,10 +4306,14 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45ryz</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>X</t>
@@ -4293,13 +4325,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="R40" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4308,12 +4340,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1242676842</t>
+          <t>1283224823</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1242676842</t>
+          <t>https://m.place.naver.com/place/1283224823</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4330,29 +4362,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>153트레이닝</t>
+          <t>바디수</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>trainerps@naver.com</t>
+          <t>lovelygodus@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1361-0679</t>
+          <t>070-8802-9000</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로3길 36 202호</t>
+          <t>경기도 성남시 분당구 서판교로44번길 15 101호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.bodysoo.co.kr/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4362,12 +4394,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4378,22 +4410,22 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q41" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R41" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4402,12 +4434,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1932735845</t>
+          <t>32497004</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1932735845</t>
+          <t>https://m.place.naver.com/place/32497004</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4424,34 +4456,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>D gym PT 수내역점</t>
+          <t>H GYM PT GT 판교2호점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>hyenggoo1@naver.com</t>
+          <t>hgym9408@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1438-1374</t>
+          <t>0507-1353-9408</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로200번길 34 205, 206호</t>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://hgym.imweb.me</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4461,7 +4493,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4471,7 +4503,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40pej</t>
+          <t>https://talk.naver.com/ct/w47alh</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4485,13 +4517,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>156</v>
+        <v>279</v>
       </c>
       <c r="Q42" t="n">
-        <v>367</v>
+        <v>422</v>
       </c>
       <c r="R42" t="n">
-        <v>523</v>
+        <v>701</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4500,12 +4532,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1234729561</t>
+          <t>1850894755</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1234729561</t>
+          <t>https://m.place.naver.com/place/1850894755</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4522,29 +4554,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>뉴로스위칭 판교본점</t>
+          <t>바른몸PT센터</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>team_hero@naver.com</t>
+          <t>wlsrkfdl1@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1403-9311</t>
+          <t>0507-1337-9711</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1A 제2층 216호</t>
+          <t>경기도 성남시 분당구 백현로101번길 20 3층 301호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wlsrkfdl1</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4554,12 +4586,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4575,17 +4607,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="R43" t="n">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4594,12 +4626,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>34896927</t>
+          <t>2090651326</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34896927</t>
+          <t>https://m.place.naver.com/place/2090651326</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4616,24 +4648,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>리조트휘트니스 PT 판교점</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>resort_5@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1438-0677</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4663,7 +4695,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ixpk</t>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4677,13 +4709,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>413</v>
+        <v>2543</v>
       </c>
       <c r="Q44" t="n">
-        <v>715</v>
+        <v>323</v>
       </c>
       <c r="R44" t="n">
-        <v>1128</v>
+        <v>2866</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4692,12 +4724,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>35524502</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35524502</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4714,34 +4746,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H GYM PT 대장3호점</t>
+          <t>휘트니스클럽S 수내점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>hgym9408@naver.com</t>
+          <t>fitnessclubs12@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1329-9408</t>
+          <t>0507-1311-1188</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로 84 304호</t>
+          <t>경기도 성남시 분당구 백현로101번길 11 5층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://hgym.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4751,7 +4783,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4761,7 +4793,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4aih7</t>
+          <t>https://talk.naver.com/ct/w49zvx</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4775,13 +4807,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>111</v>
+        <v>308</v>
       </c>
       <c r="Q45" t="n">
-        <v>111</v>
+        <v>917</v>
       </c>
       <c r="R45" t="n">
-        <v>222</v>
+        <v>1225</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4790,12 +4822,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1027491629</t>
+          <t>1228787055</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027491629</t>
+          <t>https://m.place.naver.com/place/1228787055</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4807,29 +4839,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>써트짐 PT</t>
+          <t>커스텀핏 PT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>certgym@naver.com</t>
+          <t>customfitpt@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1367-7665</t>
+          <t>031-8016-5677</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로214번길 8 207호(수내동, MS프라자)</t>
+          <t>경기도 성남시 분당구 운중로 123 마크시티 오렌지동 3층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4854,14 +4886,10 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dpxc</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>X</t>
@@ -4869,17 +4897,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>237</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>286</v>
+        <v>5</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4888,12 +4916,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1331332549</t>
+          <t>35644006</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1331332549</t>
+          <t>https://m.place.naver.com/place/35644006</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4905,29 +4933,29 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>바른몸 재활PT&amp;필라테스</t>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>wise_body_care@naver.com</t>
+          <t>halogym02@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1491-9925</t>
+          <t>0507-1315-8840</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 376 6층 605호</t>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4957,27 +4985,27 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5uzxa</t>
+          <t>https://talk.naver.com/ct/wcfevb4</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>82</v>
+        <v>663</v>
       </c>
       <c r="Q47" t="n">
-        <v>35</v>
+        <v>934</v>
       </c>
       <c r="R47" t="n">
-        <v>117</v>
+        <v>1597</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4986,12 +5014,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1253283857</t>
+          <t>1806695299</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1253283857</t>
+          <t>https://m.place.naver.com/place/1806695299</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5008,24 +5036,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>이상해GYM PT 판교역점</t>
+          <t>피티스튜디오이룸 PT EROOM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>isanghaegym@naver.com</t>
+          <t>ptstudioeroom@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1399-9644</t>
+          <t>0507-1361-7934</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 지2층 B2086호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 45 3층 303호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5055,12 +5083,12 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w1cs1tt</t>
+          <t>https://talk.naver.com/ct/wuyghv5</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -5069,13 +5097,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="Q48" t="n">
-        <v>124</v>
+        <v>32</v>
       </c>
       <c r="R48" t="n">
-        <v>191</v>
+        <v>79</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -5084,12 +5112,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1053530808</t>
+          <t>1164280530</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053530808</t>
+          <t>https://m.place.naver.com/place/1164280530</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5106,24 +5134,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>원프로짐PT</t>
+          <t>근육연구소</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>onepro_gym@naver.com</t>
+          <t>musclelab_9609@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1304-9363</t>
+          <t>0507-1492-9193</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로 164 훼미리프라자 402호</t>
+          <t>경기도 성남시 분당구 판교역로 109 A동 B212호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5148,14 +5176,10 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wd5irjz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>X</t>
@@ -5167,13 +5191,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Q49" t="n">
-        <v>36</v>
+        <v>172</v>
       </c>
       <c r="R49" t="n">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5182,12 +5206,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1663447864</t>
+          <t>1655228047</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1663447864</t>
+          <t>https://m.place.naver.com/place/1655228047</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5199,34 +5223,34 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>실내골프연습장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>철인짐</t>
+          <t>제로퍼스널트레이닝PT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>chulingym@naver.com</t>
+          <t>phh3014@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1475-0968</t>
+          <t>0507-1341-5808</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 141 우리은행 건물 9층 철인짐</t>
+          <t>경기도 성남시 분당구 운중로 115 판오션타워 501호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/hyunhwa_zero</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5236,7 +5260,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5246,17 +5270,13 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5xjbr</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5265,13 +5285,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5280,12 +5300,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1883390700</t>
+          <t>21647284</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1883390700</t>
+          <t>https://m.place.naver.com/place/21647284</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5302,29 +5322,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>블랙스미스짐 헬스PT 판교점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>emmaholic1@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1352-4388</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 판교역로 136 지하2층 비2147호, 비2148호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://blacksmithgym.kr/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5334,7 +5354,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5349,7 +5369,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi2wapb</t>
+          <t>https://talk.naver.com/ct/w41p6u</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5363,13 +5383,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2543</v>
+        <v>107</v>
       </c>
       <c r="Q51" t="n">
-        <v>323</v>
+        <v>195</v>
       </c>
       <c r="R51" t="n">
-        <v>2866</v>
+        <v>302</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5378,12 +5398,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1462760829</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1462760829</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5400,24 +5420,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>베러댄 휘트니스 분당야탑점</t>
+          <t>헬스보이짐&amp;필라걸 수내점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>56zqrwcwsv@naver.com</t>
+          <t>healthboy40@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1438-9698</t>
+          <t>0507-1380-2239</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5447,7 +5467,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4o2xj</t>
+          <t>https://talk.naver.com/ct/w4laa0</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5461,13 +5481,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>382</v>
+        <v>967</v>
       </c>
       <c r="Q52" t="n">
-        <v>2093</v>
+        <v>737</v>
       </c>
       <c r="R52" t="n">
-        <v>2475</v>
+        <v>1704</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5476,12 +5496,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1013682807</t>
+          <t>1973151166</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013682807</t>
+          <t>https://m.place.naver.com/place/1973151166</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5498,34 +5518,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H GYM PT GT 운중점</t>
+          <t>어반피트</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>hgym9408@naver.com</t>
+          <t>urbanfit_@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1344-9408</t>
+          <t>0507-1357-0997</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로188번길 8 1층</t>
+          <t>경기도 성남시 분당구 운중로 128 601,602호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://hgym.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5535,7 +5555,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5545,7 +5565,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4gmmz</t>
+          <t>https://talk.naver.com/ct/w44gs9</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5559,13 +5579,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="Q53" t="n">
-        <v>145</v>
+        <v>27</v>
       </c>
       <c r="R53" t="n">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5574,12 +5594,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1970444039</t>
+          <t>1138293980</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1970444039</t>
+          <t>https://m.place.naver.com/place/1138293980</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5596,25 +5616,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>바로선운동센터 판교점</t>
+          <t>판교피트니스센터</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>coolksh11@naver.com</t>
+          <t>towershift@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1343-5171</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
+          <t>경기도 성남시 분당구 판교로289번길 20 3층 판교피트니스센터</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/towershift</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5624,24 +5648,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wve1811</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>X</t>
@@ -5653,13 +5673,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="Q54" t="n">
-        <v>187</v>
+        <v>13</v>
       </c>
       <c r="R54" t="n">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5668,12 +5688,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2015061102</t>
+          <t>1874121479</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015061102</t>
+          <t>https://m.place.naver.com/place/1874121479</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5690,24 +5710,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>좋은습관PTSTUDIO 판교운중</t>
+          <t>뉴로스위칭 판교본점</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>goodhabitpg@naver.com</t>
+          <t>team_hero@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1480-0677</t>
+          <t>0507-1403-9311</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 6층</t>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1A 제2층 216호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5732,14 +5752,10 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5wyz9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>X</t>
@@ -5747,17 +5763,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="Q55" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="R55" t="n">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5766,12 +5782,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1070284726</t>
+          <t>34896927</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070284726</t>
+          <t>https://m.place.naver.com/place/34896927</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5788,29 +5804,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>비아핏</t>
+          <t>여성전용 비조 필라PT 자이로토닉</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>viafit@naver.com</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1379-7507</t>
-        </is>
-      </c>
+          <t>viyulgallery@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>themosttimes@tmt.co.kr</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 15-2 지하1층,지상1층</t>
+          <t>경기도 성남시 분당구 운중로 132</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.themosttimes.co.kr/43811</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5820,7 +5836,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5830,14 +5846,10 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w37pnp4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>X</t>
@@ -5845,17 +5857,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="Q56" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="R56" t="n">
-        <v>50</v>
+        <v>179</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5864,12 +5876,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1772663783</t>
+          <t>1600591794</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1772663783</t>
+          <t>https://m.place.naver.com/place/1600591794</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5881,29 +5893,29 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>제로업PT</t>
+          <t>카운터복싱 판교대장점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>linefit91@naver.com</t>
+          <t>counterboxing13@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>031-623-2775</t>
+          <t>0507-1365-8859</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 느티로 16 7층</t>
+          <t>경기도 성남시 분당구 판교대장로8길 8 303호, 304호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5928,10 +5940,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u3lu</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
           <t>X</t>
@@ -5939,17 +5955,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>772</v>
+        <v>5</v>
       </c>
       <c r="Q57" t="n">
-        <v>723</v>
+        <v>210</v>
       </c>
       <c r="R57" t="n">
-        <v>1495</v>
+        <v>215</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5958,12 +5974,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1975822360</t>
+          <t>1889442444</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1975822360</t>
+          <t>https://m.place.naver.com/place/1889442444</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5980,24 +5996,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>커스텀PT</t>
+          <t>바로선운동센터 판교점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>custom_pt@naver.com</t>
+          <t>coolksh11@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0507-1485-0376</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로779번길 48 3층 304호</t>
+          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6027,7 +6039,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4074g</t>
+          <t>https://talk.naver.com/ct/wve1811</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6041,13 +6053,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="R58" t="n">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -6056,12 +6068,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1204743611</t>
+          <t>2015061102</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1204743611</t>
+          <t>https://m.place.naver.com/place/2015061102</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6078,29 +6090,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>여성전용 비조 필라PT 자이로토닉</t>
+          <t>유앤바디PT 분당수내점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>viyulgallery@naver.com</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>themosttimes@tmt.co.kr</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>unbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>031-714-4729</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 132</t>
+          <t>경기도 성남시 분당구 백현로101번길 12 세인프라자 402호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.themosttimes.co.kr/43811</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6110,7 +6122,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6125,7 +6137,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4642d</t>
+          <t>https://talk.naver.com/ct/w4b6la</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6135,17 +6147,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="Q59" t="n">
-        <v>50</v>
+        <v>168</v>
       </c>
       <c r="R59" t="n">
-        <v>179</v>
+        <v>286</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6154,12 +6166,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1600591794</t>
+          <t>1853394852</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1600591794</t>
+          <t>https://m.place.naver.com/place/1853394852</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6176,59 +6188,59 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>바른몸PT센터</t>
+          <t>버핏그라운드 PT 판교</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>wlsrkfdl1@naver.com</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1337-9711</t>
+          <t>0507-1417-1133</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 20 3층 301호</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4frie</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6237,13 +6249,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6252,12 +6264,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2090651326</t>
+          <t>2029680813</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090651326</t>
+          <t>https://m.place.naver.com/place/2029680813</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6274,39 +6286,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>피티세븐 퍼스널트레이닝</t>
+          <t>업투 휘트니스 분당판교점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>body2balance@naver.com</t>
+          <t>uptofitness-@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1400-9428</t>
+          <t>0507-1343-8274</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://www.pts7.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6321,12 +6333,12 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4bej5</t>
+          <t>https://talk.naver.com/ct/w5ijhg</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6335,13 +6347,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>302</v>
+        <v>621</v>
       </c>
       <c r="Q61" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="R61" t="n">
-        <v>592</v>
+        <v>912</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6350,12 +6362,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>13093618</t>
+          <t>1928497638</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13093618</t>
+          <t>https://m.place.naver.com/place/1928497638</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6367,29 +6379,29 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>실내골프연습장</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스 PT 판교점</t>
+          <t>철인짐</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>halogym02@naver.com</t>
+          <t>chulingym@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1315-8840</t>
+          <t>0507-1475-0968</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+          <t>경기도 성남시 분당구 운중로 141 우리은행 건물 9층 철인짐</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6419,7 +6431,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfevb4</t>
+          <t>https://talk.naver.com/ct/w5xjbr</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6429,17 +6441,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>663</v>
+        <v>8</v>
       </c>
       <c r="Q62" t="n">
-        <v>933</v>
+        <v>12</v>
       </c>
       <c r="R62" t="n">
-        <v>1596</v>
+        <v>20</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6448,12 +6460,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1806695299</t>
+          <t>1883390700</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806695299</t>
+          <t>https://m.place.naver.com/place/1883390700</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6465,34 +6477,34 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ACS 스트레칭 판교</t>
+          <t>피티세븐 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>cldud777725@naver.com</t>
+          <t>body2balance@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1389-4127</t>
+          <t>0507-1400-9428</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 판교역푸르지오월드마크 상가1층 72호</t>
+          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.npsacs.com</t>
+          <t>http://www.pts7.com</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6502,12 +6514,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6517,7 +6529,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ijjd</t>
+          <t>https://talk.naver.com/ct/w4bej5</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6531,13 +6543,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>5</v>
+        <v>302</v>
       </c>
       <c r="Q63" t="n">
-        <v>2</v>
+        <v>290</v>
       </c>
       <c r="R63" t="n">
-        <v>7</v>
+        <v>592</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6546,12 +6558,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1136320574</t>
+          <t>13093618</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136320574</t>
+          <t>https://m.place.naver.com/place/13093618</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6568,29 +6580,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>핏앤클래시 PT</t>
+          <t>턴핏PT 판교운중점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>fitclassy22@naver.com</t>
+          <t>sungbin00@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1325-5251</t>
+          <t>031-698-4246</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로 154 낙생빌딩 201호</t>
+          <t>경기도 성남시 분당구 운중로 131 803호, 804호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitclassy22</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6600,20 +6612,24 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a9c1</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr">
         <is>
           <t>X</t>
@@ -6625,13 +6641,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="Q64" t="n">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="R64" t="n">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6640,12 +6656,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1283224823</t>
+          <t>1457398870</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283224823</t>
+          <t>https://m.place.naver.com/place/1457398870</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6662,24 +6678,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>스윗바디</t>
+          <t>엑서사이언스짐</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>superfly3@naver.com</t>
+          <t>exerscience@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>031-701-4327</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로2번길 36 1층 스윗바디</t>
+          <t>경기도 성남시 분당구 판교역로 240 삼환하이펙스A동 B1층 B117-1호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6709,7 +6721,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5whn9</t>
+          <t>https://talk.naver.com/ct/w5vur6</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -6719,17 +6731,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="Q65" t="n">
-        <v>19</v>
+        <v>143</v>
       </c>
       <c r="R65" t="n">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6738,12 +6750,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>20364482</t>
+          <t>1746641680</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20364482</t>
+          <t>https://m.place.naver.com/place/1746641680</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6760,34 +6772,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>레조나헬스랩PT 서판교점</t>
+          <t>에너지플로우짐</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>resonar_healthlab@naver.com</t>
+          <t>exerscience@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1411-1104</t>
+          <t>0507-1346-9129</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
+          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B126-1호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resonar_healthlab</t>
+          <t>https://energyflowlab.my.canva.site</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6797,7 +6809,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6817,13 +6829,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>202</v>
+        <v>38</v>
       </c>
       <c r="R66" t="n">
-        <v>258</v>
+        <v>39</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6832,12 +6844,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1644348689</t>
+          <t>1846760075</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1644348689</t>
+          <t>https://m.place.naver.com/place/1846760075</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6854,24 +6866,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>린바디핏 PT 판교본점</t>
+          <t>머슬짐 PT 분당서현점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>leanbodyfitv2@naver.com</t>
+          <t>musclegym_@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1302-8312</t>
+          <t>0507-1436-9680</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 지하113호</t>
+          <t>경기도 성남시 분당구 황새울로342번길 19 유성그린빌딩 6층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6901,27 +6913,27 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w3fqoyd</t>
+          <t>https://talk.naver.com/ct/wgye1u3</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="Q67" t="n">
-        <v>108</v>
+        <v>368</v>
       </c>
       <c r="R67" t="n">
-        <v>243</v>
+        <v>568</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6930,12 +6942,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1699238533</t>
+          <t>1208748555</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699238533</t>
+          <t>https://m.place.naver.com/place/1208748555</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -6947,34 +6959,34 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>R31 필라테스 PT 판교점</t>
+          <t>좋은습관PTSTUDIO 판교운중</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>r31functional@naver.com</t>
+          <t>goodhabitpg@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1489-0374</t>
+          <t>0507-1480-0677</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 58 나이스프라자 4층 402호</t>
+          <t>경기도 성남시 분당구 운중로 142 6층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/r31functional</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6984,20 +6996,24 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wyz9</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
           <t>X</t>
@@ -7009,13 +7025,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="Q68" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="R68" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -7024,12 +7040,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1262189356</t>
+          <t>1070284726</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1262189356</t>
+          <t>https://m.place.naver.com/place/1070284726</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -7046,24 +7062,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>어반피트</t>
+          <t>153트레이닝</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>urbanfit_@naver.com</t>
+          <t>trainerps@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1357-0997</t>
+          <t>0507-1361-0679</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 128 601,602호</t>
+          <t>경기도 성남시 분당구 판교공원로3길 36 202호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7088,32 +7104,28 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44gs9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="R69" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -7122,12 +7134,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1138293980</t>
+          <t>1932735845</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138293980</t>
+          <t>https://m.place.naver.com/place/1932735845</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7144,39 +7156,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>근육연구소</t>
+          <t>데스런 판교점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>musclelab_9609@naver.com</t>
+          <t>deslun@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1492-9193</t>
+          <t>0507-1412-6347</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 109 A동 B212호</t>
+          <t>경기도 성남시 분당구 판교역로2번길 38</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.deslun.co.kr</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7186,10 +7198,14 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ty8f</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr">
         <is>
           <t>X</t>
@@ -7201,13 +7217,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="Q70" t="n">
-        <v>172</v>
+        <v>432</v>
       </c>
       <c r="R70" t="n">
-        <v>177</v>
+        <v>454</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7216,12 +7232,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1655228047</t>
+          <t>31469573</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1655228047</t>
+          <t>https://m.place.naver.com/place/31469573</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7238,38 +7254,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 판교</t>
+          <t>뱅핏 PT 판교운중점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>bangfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1417-1133</t>
+          <t>0507-1345-4609</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+          <t>경기도 성남시 분당구 운중로 122 골드클래스 8층 801호, 802호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://www.instagram.com/bangfit_official</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7279,7 +7291,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7290,7 +7302,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7299,13 +7311,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7314,12 +7326,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>2029680813</t>
+          <t>1890400282</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
+          <t>https://m.place.naver.com/place/1890400282</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7331,38 +7343,30 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>스윕피티필라테스</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0507-1329-4325</t>
-        </is>
-      </c>
+          <t>songj1919@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 상가동 1층 105,106호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7372,12 +7376,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7387,12 +7391,12 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42raj</t>
+          <t>https://talk.naver.com/ct/wcc6zd5</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7401,13 +7405,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1765</v>
+        <v>17</v>
       </c>
       <c r="Q72" t="n">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="R72" t="n">
-        <v>2015</v>
+        <v>119</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7416,12 +7420,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1734844856</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1734844856</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7433,53 +7437,49 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교벤처타운</t>
+          <t>리조트휘트니스 PT 판교점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>resort_5@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1315-3624</t>
+          <t>0507-1438-0677</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzq100p</t>
+          <t>https://talk.naver.com/ct/w5ixpk</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7503,13 +7503,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>111</v>
+        <v>413</v>
       </c>
       <c r="Q73" t="n">
-        <v>29</v>
+        <v>715</v>
       </c>
       <c r="R73" t="n">
-        <v>140</v>
+        <v>1128</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7518,12 +7518,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>2064425838</t>
+          <t>35524502</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064425838</t>
+          <t>https://m.place.naver.com/place/35524502</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7535,44 +7535,44 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>에너지플로우짐</t>
+          <t>PDC스포츠센터</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>exerscience@naver.com</t>
+          <t>spxkzjs12@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1346-9129</t>
+          <t>031-8060-0377</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B126-1호</t>
+          <t>경기도 성남시 분당구 판교로 242 판교디지털센터 A동 2층 PDC스포츠센터</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://energyflowlab.my.canva.site</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7593,17 +7593,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="Q74" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="R74" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1846760075</t>
+          <t>1057141943</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1846760075</t>
+          <t>https://m.place.naver.com/place/1057141943</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7634,34 +7634,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>유밸런스</t>
+          <t>H GYM PT 대장3호점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>moveez@naver.com</t>
+          <t>hgym9408@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1496-8969</t>
+          <t>0507-1329-9408</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 140 203호</t>
+          <t>경기도 성남시 분당구 판교대장로 84 304호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://hgym.co.kr</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xvy6</t>
+          <t>https://talk.naver.com/ct/w4aih7</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -7695,13 +7695,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="Q75" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="R75" t="n">
-        <v>138</v>
+        <v>222</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7710,12 +7710,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1069284280</t>
+          <t>1027491629</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069284280</t>
+          <t>https://m.place.naver.com/place/1027491629</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7732,24 +7732,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>팀제이맥스 피티 서현점</t>
+          <t>베러댄 휘트니스 분당야탑점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>linefit91@naver.com</t>
+          <t>56zqrwcwsv@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>031-702-8296</t>
+          <t>0507-1438-9698</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
+          <t>경기도 성남시 분당구 야탑로75번길 15 세화빌딩 4층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7774,10 +7774,14 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o2xj</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>X</t>
@@ -7789,13 +7793,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>910</v>
+        <v>382</v>
       </c>
       <c r="Q76" t="n">
-        <v>548</v>
+        <v>2093</v>
       </c>
       <c r="R76" t="n">
-        <v>1458</v>
+        <v>2475</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7804,12 +7808,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1639683746</t>
+          <t>1013682807</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1639683746</t>
+          <t>https://m.place.naver.com/place/1013682807</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">

--- a/naver-place-crawler/results_health/판교_PT.xlsx
+++ b/naver-place-crawler/results_health/판교_PT.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>원팀짐</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>oneteamgym-@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-702-2070</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 128 7층 701호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oneteamgym1</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>493</v>
+        <v>2545</v>
       </c>
       <c r="Q2" t="n">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="R2" t="n">
-        <v>784</v>
+        <v>2868</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1973455447</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973455447</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>원팀짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
+          <t>oneteamgym-@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>031-702-2070</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 운중로 128 7층 701호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>https://www.instagram.com/oneteamgym1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>165</v>
+        <v>493</v>
       </c>
       <c r="Q3" t="n">
-        <v>144</v>
+        <v>291</v>
       </c>
       <c r="R3" t="n">
-        <v>309</v>
+        <v>784</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>1973455447</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/1973455447</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>레조나헬스랩PT 서판교점</t>
+          <t>데스런 판교점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>resonar_healthlab@naver.com</t>
+          <t>deslun@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1411-1104</t>
+          <t>0507-1412-6347</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
+          <t>경기도 성남시 분당구 판교역로2번길 38</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resonar_healthlab</t>
+          <t>http://www.deslun.co.kr</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>202</v>
+        <v>438</v>
       </c>
       <c r="R4" t="n">
-        <v>258</v>
+        <v>460</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1644348689</t>
+          <t>31469573</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1644348689</t>
+          <t>https://m.place.naver.com/place/31469573</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>리조트휘트니스 PT 판교점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>resort_5@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1438-0677</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://www.instagram.com/resortfitness__pangyo/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2545</v>
+        <v>413</v>
       </c>
       <c r="Q5" t="n">
-        <v>323</v>
+        <v>715</v>
       </c>
       <c r="R5" t="n">
-        <v>2868</v>
+        <v>1128</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>35524502</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/35524502</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>데스런 판교점</t>
+          <t>업투 휘트니스 분당판교점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>deslun@naver.com</t>
+          <t>uptofitness-@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1412-6347</t>
+          <t>0507-1343-8274</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.deslun.co.kr</t>
+          <t>https://blog.naver.com/uptofitness-</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>622</v>
       </c>
       <c r="Q6" t="n">
-        <v>437</v>
+        <v>291</v>
       </c>
       <c r="R6" t="n">
-        <v>459</v>
+        <v>913</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>31469573</t>
+          <t>1928497638</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31469573</t>
+          <t>https://m.place.naver.com/place/1928497638</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>리조트휘트니스 PT 판교점</t>
+          <t>리,무브먼트</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>resort_5@naver.com</t>
+          <t>sujin6735@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1438-0677</t>
+          <t>0507-1310-5661</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+          <t>https://www.instagram.com/re__movement</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>413</v>
+        <v>242</v>
       </c>
       <c r="Q7" t="n">
-        <v>715</v>
+        <v>246</v>
       </c>
       <c r="R7" t="n">
-        <v>1128</v>
+        <v>488</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>35524502</t>
+          <t>1149465061</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35524502</t>
+          <t>https://m.place.naver.com/place/1149465061</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>업투 휘트니스 분당판교점</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>uptofitness-@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1343-8274</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/uptofitness-</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>622</v>
+        <v>141</v>
       </c>
       <c r="Q8" t="n">
-        <v>291</v>
+        <v>1437</v>
       </c>
       <c r="R8" t="n">
-        <v>913</v>
+        <v>1578</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1928497638</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928497638</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>리,무브먼트</t>
+          <t>더바디짐 PT 분당수내점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sujin6735@naver.com</t>
+          <t>thebodyptgym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1310-5661</t>
+          <t>0507-1387-7676</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
+          <t>경기도 성남시 분당구 수내로46번길 11 대덕글로리빌딩 5층 더바디짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re__movement</t>
+          <t>https://blog.naver.com/thebodyptgym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>242</v>
+        <v>153</v>
       </c>
       <c r="Q9" t="n">
-        <v>246</v>
+        <v>1712</v>
       </c>
       <c r="R9" t="n">
-        <v>488</v>
+        <v>1865</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1149465061</t>
+          <t>36666737</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1149465061</t>
+          <t>https://m.place.naver.com/place/36666737</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>쿼드짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>quadgym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1303-9415</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://blog.naver.com/quadgym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="Q10" t="n">
-        <v>1437</v>
+        <v>103</v>
       </c>
       <c r="R10" t="n">
-        <v>1578</v>
+        <v>185</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1759307500</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1759307500</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1403,55 +1403,35 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>버핏그라운드 PT 판교</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1417-1133</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1462,12 +1442,12 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1486,12 +1466,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2029680813</t>
+          <t>2600001</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
+          <t>https://m.place.naver.com/place/2600001</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1501,36 +1481,20 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>쿼드짐</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>quadgym@naver.com</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1303-9415</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/quadgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1540,12 +1504,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1561,17 +1525,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1580,15 +1544,249 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1759307500</t>
+          <t>7167332</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759307500</t>
+          <t>https://m.place.naver.com/place/7167332</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>7258722</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7258722</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>7142668</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7142668</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>7583905</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7583905</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
